--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29926"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunbeiwang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27216419-FBE1-4B46-BBE8-B06F9BC91065}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4FB94D-D959-C946-9FBA-1A3830AF037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15980" yWindow="580" windowWidth="20680" windowHeight="20730" activeTab="2" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16240" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
   <si>
     <t>Tasks and Topics</t>
   </si>
@@ -339,12 +339,18 @@
   <si>
     <t>Timing : 9 - 11</t>
   </si>
+  <si>
+    <t>Week 11</t>
+  </si>
+  <si>
+    <t>Have fun</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -377,7 +383,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -746,18 +751,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
-  <dimension ref="A2:E21"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
+  <dimension ref="A2:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="2"/>
-    <col min="2" max="2" width="56.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29.125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2"/>
+    <col min="2" max="2" width="56.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="47.875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="10.625" style="2"/>
+    <col min="5" max="5" width="47.83203125" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="10.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -768,7 +773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -782,7 +787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -793,7 +798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -801,7 +806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -809,7 +814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -817,7 +822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -825,7 +830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -833,7 +838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -841,7 +846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -852,7 +857,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
@@ -861,6 +866,14 @@
       </c>
       <c r="E21" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +887,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97929D-AD65-4CE9-BF8E-66086023685B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -883,7 +896,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74299BF2-7816-4D37-8F2E-A4AEC8FE33CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -892,15 +905,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
-    <col min="6" max="6" width="21.75" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>28</v>
       </c>
@@ -914,7 +927,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46167</v>
       </c>
@@ -922,7 +935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46168</v>
       </c>
@@ -931,7 +944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f>A4+1</f>
         <v>46169</v>
@@ -940,7 +953,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" ref="A12" si="0">A10+1</f>
         <v>46170</v>
@@ -950,21 +963,21 @@
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" ref="A14" si="1">A12+1</f>
         <v>46171</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -972,7 +985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -980,7 +993,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -996,25 +1009,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
   <dimension ref="A12:F23"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" customWidth="1"/>
-    <col min="2" max="2" width="41.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1028,7 +1041,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1042,7 +1055,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1056,7 +1069,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1067,7 +1080,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1">
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1075,7 +1088,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1097,15 +1110,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4375F624-6CA8-4BD1-8837-D674A15E3640}">
   <dimension ref="A15:F25"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="49.125" customWidth="1"/>
+    <col min="1" max="1" width="49.1640625" customWidth="1"/>
     <col min="2" max="2" width="51.5" customWidth="1"/>
     <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:2" ht="46.5">
+    <row r="15" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1113,7 +1126,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -1121,7 +1134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -1135,7 +1148,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -1149,7 +1162,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -1163,7 +1176,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -1182,13 +1195,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E959A69-B699-4CFA-82E0-7BD72875D037}">
   <dimension ref="A15:D21"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.25" customWidth="1"/>
-    <col min="2" max="2" width="21.625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -1196,12 +1209,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -1209,7 +1222,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -1217,7 +1230,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -1233,26 +1246,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC185F-F58B-4882-BB6A-99C5A8DAD27D}">
   <dimension ref="A14:E22"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-    <col min="4" max="4" width="23.375" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -1260,7 +1273,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -1271,7 +1284,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -1285,12 +1298,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>88</v>
       </c>
@@ -1303,19 +1316,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5580AA-63C5-4A17-B275-34DB10D89DEB}">
   <dimension ref="A14:C19"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="52.375" customWidth="1"/>
+    <col min="1" max="1" width="52.33203125" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -1323,7 +1336,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1331,7 +1344,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -1347,19 +1360,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08672E17-9FFE-4DB4-AF66-56E8BA384E79}">
   <dimension ref="A14:D15"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.25" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1378,7 +1391,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C2D4C5-F861-4F4B-9751-7CF6281C8800}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1523,12 +1536,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1537,14 +1544,43 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4FB94D-D959-C946-9FBA-1A3830AF037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC25B0FA-2732-8F4F-A42B-405E159A5D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16240" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
   <si>
     <t>Tasks and Topics</t>
   </si>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>Week 10</t>
-  </si>
-  <si>
-    <t>Finalize Github, prepare for final presentation, finalize Kohl Insights</t>
   </si>
   <si>
     <t>Poster, Kohl Insights, Shiny APP</t>
@@ -340,10 +337,7 @@
     <t>Timing : 9 - 11</t>
   </si>
   <si>
-    <t>Week 11</t>
-  </si>
-  <si>
-    <t>Have fun</t>
+    <t>Finalize Github</t>
   </si>
 </sst>
 </file>
@@ -751,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
-  <dimension ref="A2:E23"/>
+  <dimension ref="A2:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="2"/>
@@ -862,18 +856,10 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -915,16 +901,16 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
         <v>28</v>
-      </c>
-      <c r="D1" t="s">
-        <v>29</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -932,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -941,7 +927,7 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -950,7 +936,7 @@
         <v>46169</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -959,7 +945,7 @@
         <v>46170</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -974,31 +960,31 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
         <v>38</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
         <v>40</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1019,87 +1005,87 @@
   <sheetData>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
       </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
       <c r="E20" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
         <v>52</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
         <v>54</v>
       </c>
-      <c r="B23" t="s">
+      <c r="E23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" t="s">
         <v>55</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1123,68 +1109,68 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
         <v>58</v>
-      </c>
-      <c r="D17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
         <v>60</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E19" t="s">
         <v>61</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>62</v>
-      </c>
-      <c r="F19" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="B21" t="s">
+      <c r="E21" t="s">
         <v>65</v>
       </c>
-      <c r="E21" t="s">
-        <v>66</v>
-      </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
         <v>67</v>
       </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
         <v>69</v>
       </c>
-      <c r="B25" t="s">
+      <c r="E25" t="s">
         <v>70</v>
-      </c>
-      <c r="E25" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1203,39 +1189,39 @@
   <sheetData>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
         <v>72</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
         <v>74</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1257,55 +1243,55 @@
   <sheetData>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
         <v>80</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
         <v>83</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>84</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1325,31 +1311,31 @@
   <sheetData>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
         <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
         <v>92</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1374,13 +1360,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
         <v>95</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1398,6 +1384,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -1535,22 +1536,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1566,21 +1569,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunbeiwang\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC25B0FA-2732-8F4F-A42B-405E159A5D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="855" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0376B6FE-DBFA-47E4-A4D0-B60A6FCC666F}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16240" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="15980" yWindow="580" windowWidth="20680" windowHeight="20730" firstSheet="3" activeTab="3" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -46,27 +46,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
-  <si>
-    <t>Tasks and Topics</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="179">
+  <si>
+    <t>Topics</t>
+  </si>
+  <si>
+    <t>Important Milestones</t>
   </si>
   <si>
     <t>Deliverables</t>
   </si>
   <si>
-    <t>Important Dates</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
-    <t>Basic Research skills</t>
-  </si>
-  <si>
-    <t>Plan</t>
-  </si>
-  <si>
-    <t>Orientation: Wednesday May 27, 2026</t>
+    <t>Onboarding and Basic Research skills</t>
+  </si>
+  <si>
+    <t>Onboarding and Project Assignment</t>
+  </si>
+  <si>
+    <t>A work plan, Git hub</t>
   </si>
   <si>
     <t>Week 2</t>
@@ -102,10 +102,16 @@
     <t>Advanced skills and topics</t>
   </si>
   <si>
+    <t>Midterm Check In with Stakeholders</t>
+  </si>
+  <si>
     <t xml:space="preserve">Week 7 </t>
   </si>
   <si>
-    <t>Analysis (start Kohl Insights)</t>
+    <t xml:space="preserve">Analysis </t>
+  </si>
+  <si>
+    <t>Begin Shiny App and start Kohl Insights</t>
   </si>
   <si>
     <t>Week 8</t>
@@ -114,178 +120,430 @@
     <t>Analysis (finalize results, make progress on Kohl Insights)</t>
   </si>
   <si>
+    <t>Deploy Version 1 of Shiny App</t>
+  </si>
+  <si>
     <t>Week 9</t>
   </si>
   <si>
     <t>Finalize R shiny + poster, make progress on Kohl Insights</t>
   </si>
   <si>
-    <t>Abstract submission deadline is July 20 at 8:00 a.m.</t>
+    <t>Abstract submission (due July 20 at 8:00 a.m.)</t>
   </si>
   <si>
     <t>Week 10</t>
   </si>
   <si>
+    <t>Finalize Github, prepare for final presentation at Summer VT Undergraduate Research Symposium, finalize Kohl Insights</t>
+  </si>
+  <si>
     <t>Poster, Kohl Insights, Shiny APP</t>
   </si>
   <si>
-    <t>Topic</t>
+    <t>Week 1: Onboarding, Project Assignment, Introduction to Research</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Event/Activities</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Event/Activities</t>
+    <t>Who</t>
+  </si>
+  <si>
+    <t>Sun, May 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move into Dorm: Check in at New Hall West for dorm assignment. </t>
+  </si>
+  <si>
+    <t>Mon, May 25</t>
   </si>
   <si>
     <t>Memorial day - no activities</t>
   </si>
   <si>
-    <t>First day</t>
+    <t>Tue, May 26</t>
+  </si>
+  <si>
+    <t>Onboarding and Introduction</t>
+  </si>
+  <si>
+    <t>Morning:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONBOARDING: 
+    -Check that the participation agrement was signed, 
+    -CITI training was complete.
+    -Eduroam access, 
+    -Network Access in building,
+    -PRE-SURVEY is complete,
+    -Sign contract for pics,
+    -Pre-Survey
+    -Q&amp;A
+  </t>
+  </si>
+  <si>
+    <t>8:00 AM - 9:00 AM</t>
+  </si>
+  <si>
+    <t>Drs. Michael Cary and Yujuan Gao</t>
+  </si>
+  <si>
+    <t>COFFEE &amp; DONUTS, Welcome Interns - introduce everyone
+    -Normand take photos</t>
+  </si>
+  <si>
+    <t>9:00 AM - 10:00 AM</t>
+  </si>
+  <si>
+    <t>Everyone</t>
+  </si>
+  <si>
+    <t>Faculty Present Projects to the Interns</t>
+  </si>
+  <si>
+    <t>10:00 AM - 12:00 PM</t>
+  </si>
+  <si>
+    <t>Drs. Le Wang, Yujuan Gao, and Michael Cary</t>
+  </si>
+  <si>
+    <t>Afternoon:</t>
+  </si>
+  <si>
+    <t>Interns meet with project teams, go over expectations and workflow</t>
+  </si>
+  <si>
+    <t>1:00 PM - 3:00 PM</t>
+  </si>
+  <si>
+    <t>Faculty Advisors and Grad Fellows</t>
+  </si>
+  <si>
+    <t>Interns work on setting up software and team communication
+   - TEAMS, GIT, Downloading Software 
+   - R, R Studio, R markdown, Data Camp
+   - Look for GIT Ruben Bramasco Video</t>
+  </si>
+  <si>
+    <t>3:00 PM - 5:00 PM</t>
+  </si>
+  <si>
+    <t>Dr. Michael Cary, Dr. Yujuan Gao, and Grad Fellows</t>
+  </si>
+  <si>
+    <t>Wed, May 27</t>
   </si>
   <si>
     <t>Orientation with University - Full Day Event</t>
   </si>
   <si>
-    <t xml:space="preserve">working with stakeholder </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instructor </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Literature Rev </t>
+    <t>Thu, May 28</t>
+  </si>
+  <si>
+    <t>Introduction to Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office hour </t>
+  </si>
+  <si>
+    <t>Grad Fellows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop - Introduction to Research </t>
+  </si>
+  <si>
+    <t>9:00 AM - 10:20 AM</t>
+  </si>
+  <si>
+    <t>Dr. Le Wang</t>
+  </si>
+  <si>
+    <t>Workshop - How to work with stakeholders</t>
+  </si>
+  <si>
+    <t>10:30 AM - 12:00 PM</t>
+  </si>
+  <si>
+    <t>Dr. Eric Kaufman</t>
+  </si>
+  <si>
+    <t>Interns work on project - discuss research question for the project</t>
+  </si>
+  <si>
+    <t>Interns work on project - discuss questions to ask stakeholders</t>
+  </si>
+  <si>
+    <t>Fri, May 29</t>
+  </si>
+  <si>
+    <t>Introduction to Literature Review and Meeting Stakeholders</t>
+  </si>
+  <si>
+    <t>Workshop - How to conduct literature review</t>
+  </si>
+  <si>
+    <t>1.5 hour</t>
+  </si>
+  <si>
+    <t>Dr. Yujuan Gao</t>
+  </si>
+  <si>
+    <t>Interns meet with Stakeholder - potential slot 1</t>
+  </si>
+  <si>
+    <t>To be scheduled</t>
+  </si>
+  <si>
+    <t>Project Team and Stakeholder</t>
+  </si>
+  <si>
+    <t>Interns work on project - search, read, and summarize literature</t>
+  </si>
+  <si>
+    <t>Deliverables:</t>
+  </si>
+  <si>
+    <t>Start a draft of literature review</t>
+  </si>
+  <si>
+    <t>A more refined research question based on literature review</t>
+  </si>
+  <si>
+    <t>Week 2: Basic Programming Training and Work on Projects</t>
+  </si>
+  <si>
+    <t>Responsible Parties</t>
+  </si>
+  <si>
+    <t>Mon, Jun 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R Basics &amp; Training  </t>
+  </si>
+  <si>
+    <t>Workshop - R Basics &amp; Training Section 1</t>
+  </si>
+  <si>
+    <t>9:00 AM - 12:00 PM</t>
+  </si>
+  <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>Nathaniel/Jesse</t>
+  </si>
+  <si>
+    <t>Interns work on DATACAMP and practice R with Project Data</t>
+  </si>
+  <si>
+    <t>1:00 PM - 4:00 PM</t>
+  </si>
+  <si>
+    <t>Grad Fellows available for questions</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Read literature and refine research question</t>
+  </si>
+  <si>
+    <t>4:00 PM - 5:00 PM</t>
+  </si>
+  <si>
+    <t>Faculty and Grad Fellows available for questions</t>
+  </si>
+  <si>
+    <t>Tue, Jun 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop - R Basics &amp; Training Section 2 </t>
+  </si>
+  <si>
+    <t>1:00 PM - 5:00 PM</t>
+  </si>
+  <si>
+    <t>Wed, Jun 3</t>
+  </si>
+  <si>
+    <t>GIT Basics &amp; Training</t>
+  </si>
+  <si>
+    <t>Workshop - GIT Basics &amp; Training</t>
+  </si>
+  <si>
+    <t>Interns work on DATACAMP and practice Git and Github: Branching, Pull Requests</t>
+  </si>
+  <si>
+    <t>Thu, Jun 4</t>
+  </si>
+  <si>
+    <t>Workshop - R Shiny and R Markdown Basics &amp; Training</t>
+  </si>
+  <si>
+    <t>Interns work on DATACAMP and practice R Shiny and R Markdown</t>
+  </si>
+  <si>
+    <t>Fri, Jun 5</t>
+  </si>
+  <si>
+    <t>Workshop - Coding Organization &amp; Standard Template</t>
+  </si>
+  <si>
+    <t>1 hr</t>
+  </si>
+  <si>
+    <t>Xiaoyi Zhao</t>
+  </si>
+  <si>
+    <t>Workshop - Organizing and Documenting Data Availability</t>
+  </si>
+  <si>
+    <t>1/2 to 1 hr</t>
+  </si>
+  <si>
+    <t>Pragati Dahal</t>
+  </si>
+  <si>
+    <t>Interns meet with Stakeholder - potential slot 2</t>
+  </si>
+  <si>
+    <t>11:00 AM - 12:00 PM</t>
+  </si>
+  <si>
+    <t>Implement organization and documentation template</t>
+  </si>
+  <si>
+    <t>Interns meet with Stakeholder - potential slot 3</t>
+  </si>
+  <si>
+    <t>3:00 PM - 4:00 PM</t>
+  </si>
+  <si>
+    <t>Push progress to GIT, make sure to follow Template</t>
+  </si>
+  <si>
+    <t>A completed draft of literature review</t>
+  </si>
+  <si>
+    <t>A simple version of R Shiny app product</t>
+  </si>
+  <si>
+    <t>Week 3: Data Skills - Multimodality</t>
+  </si>
+  <si>
+    <t>Mon, Jun 8</t>
+  </si>
+  <si>
+    <t>AI &amp; Ethics Workship and Work on data</t>
+  </si>
+  <si>
+    <t>Interns meet with Grad Fellow to Assign Weekly Tasks &amp; Check In with faculty</t>
+  </si>
+  <si>
+    <t>8:30 AM - 9:30 AM</t>
+  </si>
+  <si>
+    <t>AI &amp; Ethics</t>
+  </si>
+  <si>
+    <t>Drs. Rockwell Clancy and Elena Serrano</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Work on data and develop R-Shiny</t>
+  </si>
+  <si>
+    <t>Push progress to GIT, Make sure to follow Template, Reflection</t>
+  </si>
+  <si>
+    <t>Tue, Jun 9</t>
+  </si>
+  <si>
+    <t>Structured and Large Dataset and Work on project</t>
+  </si>
+  <si>
+    <t>Workshop - Structured and Large Dataset</t>
+  </si>
+  <si>
+    <t>2 hr</t>
+  </si>
+  <si>
+    <t>Wed, Jun 10</t>
+  </si>
+  <si>
+    <t>Transportation and Health Access Data</t>
+  </si>
+  <si>
+    <t>Workshop - Transportation and Health Access Data</t>
+  </si>
+  <si>
+    <t>Junghwan?</t>
+  </si>
+  <si>
+    <t>Thu, Jun 11</t>
+  </si>
+  <si>
+    <t>Remote Sensing Data</t>
+  </si>
+  <si>
+    <t>Workshop - Remote Sensing Data</t>
+  </si>
+  <si>
+    <t>Shao Yang's Student?</t>
+  </si>
+  <si>
+    <t>Fri, Jun 12</t>
+  </si>
+  <si>
+    <t>Text data (optional)</t>
+  </si>
+  <si>
+    <t>Progress Report</t>
+  </si>
+  <si>
+    <t>All Teams + Faculty</t>
+  </si>
+  <si>
+    <t>A more complicated R shiny app product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Week 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explorotary and Communiction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Data Visualizatio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuanyuan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explorotary analysis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced R Shiny </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Week 5 Topic : Modeling Skills </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction to Statistics </t>
   </si>
   <si>
     <t xml:space="preserve">Yujuan </t>
   </si>
   <si>
-    <t>How to work with Stakeholder  Lecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eric </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduction to Research </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. L. Wang &amp; Dr. C. Wang </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week 2 : Data and Programming </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">R  (Lecture 1 &amp; 2) </t>
-  </si>
-  <si>
-    <t>Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Dr. Cary Reach out &amp; Schedule) </t>
-  </si>
-  <si>
-    <t>9 am - 12 pm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git </t>
-  </si>
-  <si>
-    <t xml:space="preserve">R Shiny  &amp; R MD </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding Organization &amp; Standard </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xiaoyi &amp; Pragati </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template </t>
-  </si>
-  <si>
-    <t>( pending)</t>
-  </si>
-  <si>
-    <t>Communicating Datasets</t>
-  </si>
-  <si>
-    <t>Pragati - how to use AI to organize data availability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(pending) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data – Multimodality – dataset, a more complicated R shiny app (deliverable)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; Ethics </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junth 8 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stuctured AP + Large Dataset </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xiaoyi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 am - 11 pm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(The exact timing will be decided later ) </t>
-  </si>
-  <si>
-    <t>Transportation, health care access</t>
-  </si>
-  <si>
-    <t>Junghwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 am - 12 pm </t>
-  </si>
-  <si>
-    <t>remote sensing</t>
-  </si>
-  <si>
-    <t>Yang Shao</t>
-  </si>
-  <si>
-    <t>Text (web scraping + natural language processing -- CS)</t>
-  </si>
-  <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 am - 12 pm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week 4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explorotary and Communiction </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Data Visualizatio </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yuanyuan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explorotary analysis </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced R Shiny </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week 5 Topic : Modeling Skills </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduction to Statistics </t>
-  </si>
-  <si>
     <t>Reduction technique -- index building</t>
   </si>
   <si>
@@ -319,7 +577,10 @@
     <t xml:space="preserve">AI - Advanced Computing at VT </t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. C. Wang will schedule the guest speaker </t>
+    <t>https://arc.vt.edu/services/training.html</t>
+  </si>
+  <si>
+    <t>Dr. C. Wang will schedule the guest speaker, "visualizing this" sounds interesting</t>
   </si>
   <si>
     <t xml:space="preserve">LLM </t>
@@ -335,16 +596,13 @@
   </si>
   <si>
     <t>Timing : 9 - 11</t>
-  </si>
-  <si>
-    <t>Finalize Github</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -374,17 +632,64 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Aptos"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF242424"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -400,16 +705,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -745,126 +1112,135 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
-  <dimension ref="A2:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:D22"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2"/>
-    <col min="2" max="2" width="56.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="47.83203125" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="10.6640625" style="2"/>
+    <col min="1" max="1" width="10.625" style="1"/>
+    <col min="2" max="2" width="61.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:4">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30.75">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" location="'Week 1'!A1" display="Week 1" xr:uid="{9E01FC4F-1E34-C54F-92AC-B56B9CB6E3E8}"/>
+    <hyperlink ref="A4" location="'Week 1'!A1" display="Week 1" xr:uid="{9E01FC4F-1E34-C54F-92AC-B56B9CB6E3E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -873,7 +1249,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97929D-AD65-4CE9-BF8E-66086023685B}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -882,7 +1258,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74299BF2-7816-4D37-8F2E-A4AEC8FE33CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -890,101 +1266,330 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" customWidth="1"/>
-    <col min="3" max="3" width="35.5" customWidth="1"/>
-    <col min="6" max="6" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="21.25" style="9" customWidth="1"/>
+    <col min="2" max="2" width="72.125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.75" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="40.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="10.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>46167</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>46168</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" t="s">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <f>A4+1</f>
-        <v>46169</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="8"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <f t="shared" ref="A12" si="0">A10+1</f>
-        <v>46170</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <f t="shared" ref="A14" si="1">A12+1</f>
-        <v>46171</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
+      <c r="C3" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="D3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E3" s="9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="F3" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B4" s="11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="C4" s="12">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6"/>
+    <row r="6" spans="1:6">
+      <c r="A6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B6" s="13" t="s">
         <v>40</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+    </row>
+    <row r="8" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="148.5" customHeight="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1">
+      <c r="B11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1">
+      <c r="B12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="B14" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="B15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="63" customHeight="1">
+      <c r="B16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1">
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" ht="21" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="21"/>
+      <c r="B21" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="21"/>
+      <c r="B22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="21"/>
+      <c r="B23" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="21"/>
+      <c r="B24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="21"/>
+      <c r="E25" s="22"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="21"/>
+      <c r="B26" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="21"/>
+      <c r="B27" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="21"/>
+      <c r="B28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="21"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="B33" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5"/>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1">
+      <c r="B35" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="B36" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5"/>
+    <row r="38" spans="1:5"/>
+    <row r="39" spans="1:5"/>
+    <row r="40" spans="1:5"/>
+    <row r="41" spans="1:5">
+      <c r="A41" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1">
+      <c r="B42" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -994,98 +1599,606 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
-  <dimension ref="A12:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M55"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="41.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="65.375" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="41.625" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="30.625" customWidth="1"/>
+    <col min="12" max="12" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="1" spans="1:6" ht="15.75">
+      <c r="A1" s="24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75"/>
+    <row r="3" spans="1:6" ht="15.75">
+      <c r="A3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.25" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75">
+      <c r="A5" s="9"/>
+      <c r="B5" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
+      <c r="A7" s="9"/>
+      <c r="B7" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75">
+      <c r="A9" s="9"/>
+      <c r="B9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75">
+      <c r="A13" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75">
+      <c r="A16" s="15"/>
+      <c r="B16" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75">
+      <c r="A18" s="9"/>
+      <c r="B18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75">
+      <c r="A20" s="9"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75">
+      <c r="A21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75">
+      <c r="A22" s="9"/>
+      <c r="B22" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75">
+      <c r="A23" s="9"/>
+      <c r="B23" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="D23" s="9"/>
+      <c r="E23" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75">
+      <c r="A26" s="9"/>
+      <c r="B26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75">
+      <c r="A30" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="13"/>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75">
+      <c r="A31" s="21"/>
+      <c r="B31" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75">
+      <c r="A32" s="21"/>
+      <c r="B32" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="21"/>
+      <c r="E32" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="F32" s="21"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75">
+      <c r="A33" s="21"/>
+      <c r="B33" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="1:13" ht="18.75" customHeight="1">
+      <c r="A34" s="21"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="9"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" ht="15.75">
+      <c r="A35" s="21"/>
+      <c r="B35" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75">
+      <c r="A36" s="21"/>
+      <c r="B36" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75">
+      <c r="A37" s="21"/>
+      <c r="B37" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75">
+      <c r="A38" s="21"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.75">
+      <c r="A39" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75">
+      <c r="A40" s="9"/>
+      <c r="B40" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="21"/>
+      <c r="E41" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F41" s="9"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" s="9"/>
+    </row>
+    <row r="43" spans="1:13" ht="15.75">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" s="9"/>
+    </row>
+    <row r="44" spans="1:13" ht="15.75">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="9"/>
+    </row>
+    <row r="45" spans="1:13" ht="15.75">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+    </row>
+    <row r="46" spans="1:13" ht="15.75">
+      <c r="A46" s="9"/>
+      <c r="B46" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+    </row>
+    <row r="47" spans="1:13" ht="15.75">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="9" t="s">
         <v>55</v>
+      </c>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F47" s="9"/>
+    </row>
+    <row r="48" spans="1:13" ht="15.75">
+      <c r="B48" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75">
+      <c r="B49" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75"/>
+    <row r="52" spans="1:5" ht="15.75"/>
+    <row r="53" spans="1:5" ht="15.75">
+      <c r="A53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75">
+      <c r="B54" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="B55" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1095,84 +2208,516 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4375F624-6CA8-4BD1-8837-D674A15E3640}">
-  <dimension ref="A15:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="49.1640625" customWidth="1"/>
-    <col min="2" max="2" width="51.5" customWidth="1"/>
-    <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="33.25" customWidth="1"/>
+    <col min="2" max="2" width="68.375" customWidth="1"/>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" t="s">
+    <row r="1" spans="1:6" ht="15.75">
+      <c r="A1" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75">
+      <c r="A3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75">
+      <c r="A4" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75">
+      <c r="A5" s="9"/>
+      <c r="B5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
+      <c r="A6" s="9"/>
+      <c r="B6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
+      <c r="A7" s="9"/>
+      <c r="B7" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75">
+      <c r="A9" s="9"/>
+      <c r="B9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75">
+      <c r="A11" s="9"/>
+      <c r="B11" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" t="s">
-        <v>70</v>
-      </c>
-    </row>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75">
+      <c r="A12" s="9"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75">
+      <c r="A13" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75">
+      <c r="A16" s="15"/>
+      <c r="B16" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75">
+      <c r="A18" s="9"/>
+      <c r="B18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75">
+      <c r="A20" s="9"/>
+      <c r="B20" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75">
+      <c r="A21" s="9"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75">
+      <c r="A22" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75">
+      <c r="A23" s="9"/>
+      <c r="B23" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75">
+      <c r="A26" s="9"/>
+      <c r="B26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75">
+      <c r="A28" s="9"/>
+      <c r="B28" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75">
+      <c r="A30" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75">
+      <c r="A31" s="21"/>
+      <c r="B31" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75">
+      <c r="A32" s="21"/>
+      <c r="B32" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75">
+      <c r="A33" s="21"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75">
+      <c r="A34" s="21"/>
+      <c r="B34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75">
+      <c r="A35" s="21"/>
+      <c r="B35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75">
+      <c r="A36" s="21"/>
+      <c r="B36" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75">
+      <c r="A37" s="21"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75">
+      <c r="A38" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75">
+      <c r="A39" s="9"/>
+      <c r="B39" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F40" s="9"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75">
+      <c r="A42" s="9"/>
+      <c r="B42" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F43" s="9"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75">
+      <c r="B44" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="15.75">
+      <c r="B65" s="4"/>
+    </row>
+    <row r="76" spans="2:2" ht="15.75"/>
+    <row r="77" spans="2:2" ht="15.75"/>
+    <row r="78" spans="2:2" ht="15.75"/>
+    <row r="82" ht="15.75"/>
+    <row r="83" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1181,47 +2726,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E959A69-B699-4CFA-82E0-7BD72875D037}">
   <dimension ref="A15:D21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="25.1640625" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="27.375" customWidth="1"/>
+    <col min="2" max="2" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="D16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1232,66 +2777,66 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC185F-F58B-4882-BB6A-99C5A8DAD27D}">
   <dimension ref="A14:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="32.5" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="23.375" customWidth="1"/>
+    <col min="5" max="5" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="D15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="B21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="B22" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1302,43 +2847,49 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5580AA-63C5-4A17-B275-34DB10D89DEB}">
   <dimension ref="A14:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="52.33203125" customWidth="1"/>
+    <col min="1" max="1" width="52.375" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>171</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B16" r:id="rId1" xr:uid="{8A601CC2-3024-4142-BA07-83583762CB46}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1346,27 +2897,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08672E17-9FFE-4DB4-AF66-56E8BA384E79}">
   <dimension ref="A14:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1377,28 +2928,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C2D4C5-F861-4F4B-9751-7CF6281C8800}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -1536,37 +3072,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunbeiwang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="855" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0376B6FE-DBFA-47E4-A4D0-B60A6FCC666F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5588140-8877-C846-B2CC-FE72DB50C19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15980" yWindow="580" windowWidth="20680" windowHeight="20730" firstSheet="3" activeTab="3" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16240" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -135,9 +135,6 @@
     <t>Week 10</t>
   </si>
   <si>
-    <t>Finalize Github, prepare for final presentation at Summer VT Undergraduate Research Symposium, finalize Kohl Insights</t>
-  </si>
-  <si>
     <t>Poster, Kohl Insights, Shiny APP</t>
   </si>
   <si>
@@ -597,12 +594,15 @@
   <si>
     <t>Timing : 9 - 11</t>
   </si>
+  <si>
+    <t>Finalize Github</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -635,28 +635,31 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -670,6 +673,7 @@
       <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1113,17 +1117,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="1"/>
-    <col min="2" max="2" width="61.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="47.875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="10.6640625" style="1"/>
+    <col min="2" max="2" width="61.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1148,7 +1152,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1159,7 +1163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1167,7 +1171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1175,7 +1179,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1183,7 +1187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -1194,7 +1198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1205,7 +1209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1216,7 +1220,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
@@ -1227,15 +1231,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30.75">
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1253,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97929D-AD65-4CE9-BF8E-66086023685B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1258,7 +1262,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74299BF2-7816-4D37-8F2E-A4AEC8FE33CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1267,51 +1271,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.25" style="9" customWidth="1"/>
-    <col min="2" max="2" width="72.125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.75" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="40.75" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="10.625" style="9"/>
+    <col min="1" max="1" width="21.1640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="72.1640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="10.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="9" t="s">
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="C4" s="12">
         <v>0.52083333333333337</v>
@@ -1320,131 +1324,131 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6"/>
-    <row r="6" spans="1:6">
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="21.75" customHeight="1">
+    <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="21.75" customHeight="1">
+    <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
       <c r="B9" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="148.5" customHeight="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="18" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="18" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1">
-      <c r="B11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="E11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="9" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1">
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1"/>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="B14" s="16" t="s">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="9" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="18" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="63" customHeight="1">
-      <c r="B16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="20.25" customHeight="1">
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
     </row>
-    <row r="18" spans="1:7" ht="21" customHeight="1">
+    <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>60</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>61</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>62</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="20"/>
       <c r="F20" s="13"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
@@ -1452,144 +1456,144 @@
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
       <c r="B22" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="E25" s="22"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="21"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="10" t="s">
+      <c r="B30" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>75</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B31" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="9" t="s">
+    </row>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="9" t="s">
+    </row>
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" s="9" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="34" spans="1:5"/>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1">
-      <c r="B35" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="B36" s="9" t="s">
+      <c r="E36" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5"/>
-    <row r="38" spans="1:5"/>
-    <row r="39" spans="1:5"/>
-    <row r="40" spans="1:5"/>
-    <row r="41" spans="1:5">
-      <c r="A41" s="9" t="s">
+      <c r="B41" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="9" t="s">
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="9" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1">
-      <c r="B42" s="9" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1600,96 +1604,95 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
   <dimension ref="A1:M55"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" customWidth="1"/>
-    <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="41.625" customWidth="1"/>
-    <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="30.625" customWidth="1"/>
-    <col min="12" max="12" width="20.75" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="65.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="41.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75"/>
-    <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>87</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.25" customHeight="1">
+    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>88</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>93</v>
-      </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1697,45 +1700,45 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1743,59 +1746,59 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>93</v>
-      </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:13" ht="15.75">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1803,31 +1806,31 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:13" ht="15.75">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:13" ht="15.75">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
@@ -1835,12 +1838,12 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:13" ht="15.75">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>104</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -1848,47 +1851,47 @@
       <c r="F21" s="13"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>93</v>
-      </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1896,45 +1899,45 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1942,12 +1945,12 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -1955,48 +1958,48 @@
       <c r="F30" s="13"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F32" s="21"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" ht="15.75">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>93</v>
-      </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:13" ht="18.75" customHeight="1">
+    <row r="34" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -2005,45 +2008,45 @@
       <c r="F34" s="9"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" ht="15.75">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" spans="1:13" ht="15.75">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:13" ht="15.75">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:13" ht="15.75">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -2051,85 +2054,85 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:13" ht="15.75">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
     </row>
-    <row r="40" spans="1:13" ht="15.75">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="9"/>
       <c r="B40" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" spans="1:13" ht="15.75">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:13" ht="15.75">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:13" ht="15.75">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:13" ht="15.75">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -2137,68 +2140,66 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
       <c r="B47" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F47" s="9"/>
     </row>
-    <row r="48" spans="1:13" ht="15.75">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="15.75">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B49" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
         <v>122</v>
       </c>
-      <c r="C49" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15.75"/>
-    <row r="52" spans="1:5" ht="15.75"/>
-    <row r="53" spans="1:5" ht="15.75">
-      <c r="A53" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15.75">
-      <c r="B54" t="s">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="B55" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2208,93 +2209,93 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4375F624-6CA8-4BD1-8837-D674A15E3640}">
-  <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <dimension ref="A1:F65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.25" customWidth="1"/>
-    <col min="2" max="2" width="68.375" customWidth="1"/>
-    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="68.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="28.625" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="E3" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>127</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -2302,97 +2303,97 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="25"/>
       <c r="C12" s="25"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>134</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>135</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2400,44 +2401,44 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -2445,43 +2446,43 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>139</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2489,44 +2490,44 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -2534,43 +2535,43 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>142</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>143</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="20"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -2578,44 +2579,44 @@
       <c r="E33" s="22"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -2623,43 +2624,43 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" s="13" t="s">
         <v>146</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>147</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="9"/>
       <c r="B39" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="9"/>
       <c r="B40" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -2667,57 +2668,52 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B44" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="15.75">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B65" s="4"/>
     </row>
-    <row r="76" spans="2:2" ht="15.75"/>
-    <row r="77" spans="2:2" ht="15.75"/>
-    <row r="78" spans="2:2" ht="15.75"/>
-    <row r="82" ht="15.75"/>
-    <row r="83" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2726,47 +2722,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E959A69-B699-4CFA-82E0-7BD72875D037}">
   <dimension ref="A15:D21"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.375" customWidth="1"/>
-    <col min="2" max="2" width="21.625" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" t="s">
         <v>151</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="D16" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>154</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>156</v>
       </c>
-      <c r="B19" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>157</v>
-      </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2777,66 +2773,66 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC185F-F58B-4882-BB6A-99C5A8DAD27D}">
   <dimension ref="A14:E22"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-    <col min="4" max="4" width="23.375" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="D15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>159</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>161</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>162</v>
       </c>
-      <c r="D18" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>164</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>165</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>166</v>
       </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="B21" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="B22" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2847,43 +2843,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5580AA-63C5-4A17-B275-34DB10D89DEB}">
   <dimension ref="A14:C19"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="52.375" customWidth="1"/>
+    <col min="1" max="1" width="52.33203125" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75">
-      <c r="A16" t="s">
+      <c r="B16" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" t="s">
         <v>172</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="C18" t="s">
         <v>174</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>176</v>
-      </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2897,27 +2893,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08672E17-9FFE-4DB4-AF66-56E8BA384E79}">
   <dimension ref="A14:D15"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.25" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" t="s">
         <v>177</v>
-      </c>
-      <c r="B15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" t="s">
-        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2928,13 +2924,28 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C2D4C5-F861-4F4B-9751-7CF6281C8800}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -3072,29 +3083,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5588140-8877-C846-B2CC-FE72DB50C19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B9FB07-3819-9142-BC2F-712B2EA14462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16240" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
@@ -595,7 +595,7 @@
     <t>Timing : 9 - 11</t>
   </si>
   <si>
-    <t>Finalize Github</t>
+    <t>Finalize Github , prepare for final presentation at Summer VT Undergraduate Research Symposium, finalize Kohl Insights</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1231,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -2931,21 +2931,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -3083,24 +3068,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3116,4 +3099,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B9FB07-3819-9142-BC2F-712B2EA14462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98B45EF-64A3-584F-A27E-68EF9EFC7606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16240" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16240" activeTab="1" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -1270,10 +1270,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="60.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="72.1640625" style="9" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" style="9" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" style="9" customWidth="1"/>
@@ -1587,12 +1587,14 @@
       <c r="A41" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="9" t="s">
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="9" t="s">
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2193,12 +2195,12 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
+      <c r="A54" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
+      <c r="A55" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3069,18 +3071,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3102,18 +3104,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7470C5D0-0E4D-6A44-9D4B-810C1203CEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11445E89-283B-2749-A9B1-22ABAA6C1D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16220" activeTab="2" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16220" activeTab="1" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -1270,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="60.83203125" style="9" bestFit="1" customWidth="1"/>
@@ -1587,14 +1587,12 @@
       <c r="A41" s="9" t="s">
         <v>82</v>
       </c>
+      <c r="B41" s="9" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9" t="s">
+      <c r="B42" s="9" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1605,7 +1603,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
@@ -2193,14 +2191,12 @@
       <c r="A53" t="s">
         <v>82</v>
       </c>
+      <c r="B53" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="B54" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2933,6 +2929,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -3070,22 +3081,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3101,21 +3114,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11445E89-283B-2749-A9B1-22ABAA6C1D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDA2753-2B25-EB44-B35A-AB5A50973BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16220" activeTab="1" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="180">
   <si>
     <t>Topics</t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>Sun, May 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move into Dorm: Check in at New Hall West for dorm assignment. </t>
   </si>
   <si>
     <t>Mon, May 25</t>
@@ -596,6 +593,12 @@
   </si>
   <si>
     <t>Finalize Github , prepare for final presentation at Summer VT Undergraduate Research Symposium, finalize Kohl Insights</t>
+  </si>
+  <si>
+    <t>Move into Dorm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check in at New Hall West for dorm assignment. </t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1239,7 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -1315,7 +1318,7 @@
         <v>36</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="C4" s="12">
         <v>0.52083333333333337</v>
@@ -1324,13 +1327,17 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -1339,10 +1346,10 @@
     </row>
     <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -1352,69 +1359,69 @@
     <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
       <c r="B9" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>44</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="E11" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>57</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1423,10 +1430,10 @@
     </row>
     <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -1435,10 +1442,10 @@
     </row>
     <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -1448,7 +1455,7 @@
     <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
@@ -1459,14 +1466,14 @@
     <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
       <c r="B22" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
@@ -1474,25 +1481,25 @@
     <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="27" t="s">
         <v>69</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1502,25 +1509,25 @@
     <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1528,10 +1535,10 @@
     </row>
     <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>74</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -1540,43 +1547,43 @@
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B31" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
@@ -1585,15 +1592,15 @@
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1617,7 +1624,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1634,7 +1641,7 @@
         <v>34</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
@@ -1642,10 +1649,10 @@
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>87</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>88</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -1655,7 +1662,7 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1665,30 +1672,30 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="F7" s="9"/>
     </row>
@@ -1703,7 +1710,7 @@
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1713,28 +1720,28 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F11" s="9"/>
     </row>
@@ -1748,10 +1755,10 @@
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -1761,7 +1768,7 @@
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1771,30 +1778,30 @@
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -1809,7 +1816,7 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -1819,14 +1826,14 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="9"/>
     </row>
@@ -1840,10 +1847,10 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>102</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>103</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -1854,7 +1861,7 @@
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1864,30 +1871,30 @@
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -1902,7 +1909,7 @@
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -1912,28 +1919,28 @@
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F28" s="9"/>
     </row>
@@ -1947,10 +1954,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -1961,7 +1968,7 @@
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
@@ -1971,14 +1978,14 @@
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F32" s="21"/>
       <c r="M32" s="3"/>
@@ -1986,16 +1993,16 @@
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="F33" s="9"/>
     </row>
@@ -2011,7 +2018,7 @@
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -2021,28 +2028,28 @@
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F36" s="9"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F37" s="9"/>
     </row>
@@ -2056,10 +2063,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -2069,7 +2076,7 @@
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="9"/>
       <c r="B40" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -2079,56 +2086,56 @@
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F41" s="9"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>111</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>114</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F44" s="9"/>
     </row>
@@ -2143,7 +2150,7 @@
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -2153,51 +2160,51 @@
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
       <c r="B47" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F47" s="9"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>120</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B49" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2220,7 +2227,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2237,7 +2244,7 @@
         <v>34</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
@@ -2245,10 +2252,10 @@
     </row>
     <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>125</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>126</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -2258,7 +2265,7 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -2268,28 +2275,28 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7" s="9"/>
     </row>
@@ -2304,7 +2311,7 @@
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -2314,27 +2321,27 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="9"/>
     </row>
@@ -2347,10 +2354,10 @@
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>133</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>134</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -2360,7 +2367,7 @@
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -2370,21 +2377,21 @@
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>136</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -2402,7 +2409,7 @@
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -2412,27 +2419,27 @@
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="9"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" s="9"/>
     </row>
@@ -2446,10 +2453,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>137</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2459,7 +2466,7 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -2469,14 +2476,14 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -2491,7 +2498,7 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -2501,27 +2508,27 @@
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F28" s="9"/>
     </row>
@@ -2535,10 +2542,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -2548,7 +2555,7 @@
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
@@ -2558,14 +2565,14 @@
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F32" s="9"/>
     </row>
@@ -2580,7 +2587,7 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -2590,27 +2597,27 @@
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F35" s="9"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F36" s="9"/>
     </row>
@@ -2624,10 +2631,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>146</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -2637,7 +2644,7 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="9"/>
       <c r="B39" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -2647,14 +2654,14 @@
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="9"/>
       <c r="B40" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F40" s="9"/>
     </row>
@@ -2669,7 +2676,7 @@
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -2679,34 +2686,34 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B44" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.2">
@@ -2728,39 +2735,39 @@
   <sheetData>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" t="s">
         <v>150</v>
-      </c>
-      <c r="B15" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" t="s">
         <v>153</v>
-      </c>
-      <c r="B17" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2782,55 +2789,55 @@
   <sheetData>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" t="s">
         <v>158</v>
-      </c>
-      <c r="B16" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" t="s">
         <v>160</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>161</v>
-      </c>
-      <c r="D18" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" t="s">
         <v>163</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>164</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>165</v>
-      </c>
-      <c r="E20" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2850,34 +2857,34 @@
   <sheetData>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" t="s">
         <v>171</v>
-      </c>
-      <c r="C16" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" t="s">
         <v>173</v>
-      </c>
-      <c r="C18" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2905,13 +2912,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" t="s">
         <v>176</v>
-      </c>
-      <c r="B15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2929,21 +2936,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -3081,24 +3073,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3114,4 +3104,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunbeiwang\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDA2753-2B25-EB44-B35A-AB5A50973BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1173" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31698AAF-FD04-4466-9B80-BC349D3B273E}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16220" activeTab="1" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="15980" yWindow="580" windowWidth="20680" windowHeight="20730" firstSheet="5" activeTab="5" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="238">
   <si>
     <t>Topics</t>
   </si>
@@ -87,13 +87,13 @@
     <t>Week 4</t>
   </si>
   <si>
-    <t>Data skills - multimodlity</t>
+    <t>Data Exploratory skills</t>
   </si>
   <si>
     <t>Week 5</t>
   </si>
   <si>
-    <t>Data Exploratory skills &amp; Modeling skills</t>
+    <t>Data Modeling skills</t>
   </si>
   <si>
     <t>Week 6</t>
@@ -135,6 +135,9 @@
     <t>Week 10</t>
   </si>
   <si>
+    <t>Finalize Github, prepare for final presentation at Summer VT Undergraduate Research Symposium, finalize Kohl Insights</t>
+  </si>
+  <si>
     <t>Poster, Kohl Insights, Shiny APP</t>
   </si>
   <si>
@@ -153,10 +156,13 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Who</t>
+    <t>Responsible Parties</t>
   </si>
   <si>
     <t>Sun, May 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move into Dorm: Check in at New Hall West for dorm assignment. </t>
   </si>
   <si>
     <t>Mon, May 25</t>
@@ -292,19 +298,37 @@
     <t>Dr. Yujuan Gao</t>
   </si>
   <si>
+    <t>Interns work on project - search, read, and summarize literature</t>
+  </si>
+  <si>
     <t>Interns meet with Stakeholder - potential slot 1</t>
   </si>
   <si>
-    <t>To be scheduled</t>
+    <t>1:00 PM - 2:00 PM</t>
   </si>
   <si>
     <t>Project Team and Stakeholder</t>
   </si>
   <si>
-    <t>Interns work on project - search, read, and summarize literature</t>
-  </si>
-  <si>
-    <t>Deliverables:</t>
+    <t>Interns meet with Stakeholder - potential slot 2</t>
+  </si>
+  <si>
+    <t>2:00 PM - 3:00 PM</t>
+  </si>
+  <si>
+    <t>Interns meet with Stakeholder - potential slot 3</t>
+  </si>
+  <si>
+    <t>3:00 PM - 4:00 PM</t>
+  </si>
+  <si>
+    <t>Interns work on project - start a draft of literature review</t>
+  </si>
+  <si>
+    <t>4:00 PM - 5:00 PM</t>
+  </si>
+  <si>
+    <t>Week 1 Deliverables:</t>
   </si>
   <si>
     <t>Start a draft of literature review</t>
@@ -316,9 +340,6 @@
     <t>Week 2: Basic Programming Training and Work on Projects</t>
   </si>
   <si>
-    <t>Responsible Parties</t>
-  </si>
-  <si>
     <t>Mon, Jun 1</t>
   </si>
   <si>
@@ -340,120 +361,147 @@
     <t>Interns work on DATACAMP and practice R with Project Data</t>
   </si>
   <si>
+    <t>1:00 PM - 3:30 PM</t>
+  </si>
+  <si>
+    <t>Grad Fellows available for questions</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Read literature and refine research question</t>
+  </si>
+  <si>
+    <t>3:30 PM - 5:00 PM</t>
+  </si>
+  <si>
+    <t>Faculty and Grad Fellows available for questions</t>
+  </si>
+  <si>
+    <t>Tue, Jun 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop - R Basics &amp; Training Section 2 </t>
+  </si>
+  <si>
+    <t>Interns work on Project - Draft literature review</t>
+  </si>
+  <si>
+    <t>Wed, Jun 3</t>
+  </si>
+  <si>
+    <t>GIT Basics &amp; Training</t>
+  </si>
+  <si>
+    <t>Workshop - GIT Basics &amp; Training</t>
+  </si>
+  <si>
+    <t>Interns work on DATACAMP and practice Git and Github: Branching, Pull Requests</t>
+  </si>
+  <si>
+    <t>Thu, Jun 4</t>
+  </si>
+  <si>
+    <t>R Shiny and Markdown Basic Training</t>
+  </si>
+  <si>
+    <t>Workshop - R Shiny and R Markdown Basics &amp; Training</t>
+  </si>
+  <si>
+    <t>Interns work on DATACAMP and practice R Shiny and R Markdown</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Build a simple version of R Shiny app for project</t>
+  </si>
+  <si>
+    <t>Fri, Jun 5</t>
+  </si>
+  <si>
+    <t>Organization and Template</t>
+  </si>
+  <si>
+    <t>Workshop - Coding Organization &amp; Standard Template</t>
+  </si>
+  <si>
+    <t>1 hr</t>
+  </si>
+  <si>
+    <t>Xiaoyi Zhao</t>
+  </si>
+  <si>
+    <t>Workshop - Organizing and Documenting Data Availability</t>
+  </si>
+  <si>
+    <t>1/2 to 1 hr</t>
+  </si>
+  <si>
+    <t>Pragati Dahal</t>
+  </si>
+  <si>
+    <t>Interns implement organization and documentation template</t>
+  </si>
+  <si>
+    <t>11:00 AM - 12:00 PM</t>
+  </si>
+  <si>
+    <t>Interns meet with Stakeholder - potential Slot 4</t>
+  </si>
+  <si>
+    <t>Interns meet with Stakeholder - potential Slot 5</t>
+  </si>
+  <si>
+    <t>Interns meet with Stakeholder - potential slot 6</t>
+  </si>
+  <si>
+    <t>Push progress to GIT, make sure to follow Template, reflect</t>
+  </si>
+  <si>
+    <t>Week 2 Deliverables:</t>
+  </si>
+  <si>
+    <t>A completed draft of literature review</t>
+  </si>
+  <si>
+    <t>A simple version of R Shiny app product</t>
+  </si>
+  <si>
+    <t>Completion of DATACAMP</t>
+  </si>
+  <si>
+    <t>Week 3: Data Skills - Multimodality</t>
+  </si>
+  <si>
+    <t>Mon, Jun 8</t>
+  </si>
+  <si>
+    <t>AI &amp; Ethics Workship and Work on data</t>
+  </si>
+  <si>
+    <t>Grad Fellows meet with faculty leads to plan for the week</t>
+  </si>
+  <si>
+    <t>8:00 AM - 8:30 AM</t>
+  </si>
+  <si>
+    <t>Drs. Michael Cary and Yujuan Gao, Grad Fellows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grad Fellow meet with interns to Assign Weekly Tasks </t>
+  </si>
+  <si>
+    <t>8:30 AM - 9:30 AM</t>
+  </si>
+  <si>
+    <t>AI &amp; Ethics</t>
+  </si>
+  <si>
+    <t>Drs. Rockwell Clancy and Elena Serrano</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Work on data and develop R-Shiny</t>
+  </si>
+  <si>
     <t>1:00 PM - 4:00 PM</t>
   </si>
   <si>
-    <t>Grad Fellows available for questions</t>
-  </si>
-  <si>
-    <t>Interns work on Project - Read literature and refine research question</t>
-  </si>
-  <si>
-    <t>4:00 PM - 5:00 PM</t>
-  </si>
-  <si>
-    <t>Faculty and Grad Fellows available for questions</t>
-  </si>
-  <si>
-    <t>Tue, Jun 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshop - R Basics &amp; Training Section 2 </t>
-  </si>
-  <si>
-    <t>1:00 PM - 5:00 PM</t>
-  </si>
-  <si>
-    <t>Wed, Jun 3</t>
-  </si>
-  <si>
-    <t>GIT Basics &amp; Training</t>
-  </si>
-  <si>
-    <t>Workshop - GIT Basics &amp; Training</t>
-  </si>
-  <si>
-    <t>Interns work on DATACAMP and practice Git and Github: Branching, Pull Requests</t>
-  </si>
-  <si>
-    <t>Thu, Jun 4</t>
-  </si>
-  <si>
-    <t>Workshop - R Shiny and R Markdown Basics &amp; Training</t>
-  </si>
-  <si>
-    <t>Interns work on DATACAMP and practice R Shiny and R Markdown</t>
-  </si>
-  <si>
-    <t>Fri, Jun 5</t>
-  </si>
-  <si>
-    <t>Workshop - Coding Organization &amp; Standard Template</t>
-  </si>
-  <si>
-    <t>1 hr</t>
-  </si>
-  <si>
-    <t>Xiaoyi Zhao</t>
-  </si>
-  <si>
-    <t>Workshop - Organizing and Documenting Data Availability</t>
-  </si>
-  <si>
-    <t>1/2 to 1 hr</t>
-  </si>
-  <si>
-    <t>Pragati Dahal</t>
-  </si>
-  <si>
-    <t>Interns meet with Stakeholder - potential slot 2</t>
-  </si>
-  <si>
-    <t>11:00 AM - 12:00 PM</t>
-  </si>
-  <si>
-    <t>Implement organization and documentation template</t>
-  </si>
-  <si>
-    <t>Interns meet with Stakeholder - potential slot 3</t>
-  </si>
-  <si>
-    <t>3:00 PM - 4:00 PM</t>
-  </si>
-  <si>
-    <t>Push progress to GIT, make sure to follow Template</t>
-  </si>
-  <si>
-    <t>A completed draft of literature review</t>
-  </si>
-  <si>
-    <t>A simple version of R Shiny app product</t>
-  </si>
-  <si>
-    <t>Week 3: Data Skills - Multimodality</t>
-  </si>
-  <si>
-    <t>Mon, Jun 8</t>
-  </si>
-  <si>
-    <t>AI &amp; Ethics Workship and Work on data</t>
-  </si>
-  <si>
-    <t>Interns meet with Grad Fellow to Assign Weekly Tasks &amp; Check In with faculty</t>
-  </si>
-  <si>
-    <t>8:30 AM - 9:30 AM</t>
-  </si>
-  <si>
-    <t>AI &amp; Ethics</t>
-  </si>
-  <si>
-    <t>Drs. Rockwell Clancy and Elena Serrano</t>
-  </si>
-  <si>
-    <t>Interns work on Project - Work on data and develop R-Shiny</t>
-  </si>
-  <si>
     <t>Push progress to GIT, Make sure to follow Template, Reflection</t>
   </si>
   <si>
@@ -499,72 +547,209 @@
     <t>Text data (optional)</t>
   </si>
   <si>
+    <t>Prepare for progress report</t>
+  </si>
+  <si>
+    <t>8:00 AM - 10:00 AM</t>
+  </si>
+  <si>
+    <t>Progress Report (10-15 minute presentation followed by 5-10 minutes Q&amp;A)</t>
+  </si>
+  <si>
+    <t>All Teams + Faculty</t>
+  </si>
+  <si>
+    <t>Week 3 Deliverables:</t>
+  </si>
+  <si>
+    <t>A more complicated R shiny app product</t>
+  </si>
+  <si>
+    <t>Week 4: Data Exploratory Skills</t>
+  </si>
+  <si>
+    <t>Mon, Jun 15</t>
+  </si>
+  <si>
+    <t>Advanced Data Visualization</t>
+  </si>
+  <si>
+    <t>Workshop - Advanced Data Visualization</t>
+  </si>
+  <si>
+    <t>1.5 hr</t>
+  </si>
+  <si>
+    <t>Yuanyuan Wen</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Work on data and advanced data visualization</t>
+  </si>
+  <si>
+    <t>Interns draft data section and communicate data visualization patterns</t>
+  </si>
+  <si>
+    <t>Tue, Jun 16</t>
+  </si>
+  <si>
+    <t>Exploratory Analysis</t>
+  </si>
+  <si>
+    <t>Workshop - Exploratory analysis</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Work on data and conduct exploratory analysis</t>
+  </si>
+  <si>
+    <t>Interns draft data section and exploratory analysis</t>
+  </si>
+  <si>
+    <t>Wed, Jun 17</t>
+  </si>
+  <si>
+    <t>Advanced R Shiny</t>
+  </si>
+  <si>
+    <t>Workshop - Advanced R Shiny</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Work on data and develop advanced R-Shiny</t>
+  </si>
+  <si>
+    <t>Interns draft data section and descriptive statistics</t>
+  </si>
+  <si>
+    <t>Thu, Jun 18</t>
+  </si>
+  <si>
+    <t>Project Work</t>
+  </si>
+  <si>
     <t>Progress Report</t>
   </si>
   <si>
-    <t>All Teams + Faculty</t>
-  </si>
-  <si>
-    <t>A more complicated R shiny app product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week 4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explorotary and Communiction </t>
+    <t>Fri, Jun 19</t>
+  </si>
+  <si>
+    <t>Juneteenth holiday - no activities</t>
+  </si>
+  <si>
+    <t>Week 4 Deliverables:</t>
+  </si>
+  <si>
+    <t>A more advanced R Shiny App product</t>
+  </si>
+  <si>
+    <t>A draft of data section and descriptive statistics</t>
+  </si>
+  <si>
+    <t>Week 5: Data Modeling Skills</t>
+  </si>
+  <si>
+    <t>Mon, Jun 22</t>
+  </si>
+  <si>
+    <t>Introduction to Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grad Fellow meet with interns to assign weekly tasks </t>
+  </si>
+  <si>
+    <t>8:30 AM - 9:00 AM</t>
+  </si>
+  <si>
+    <t>Workshop - Introduction to Statistics
+    - Hypothesis testing
+    - Common statistical models: regression and classification</t>
+  </si>
+  <si>
+    <t>3 hr</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Work on basic statistical modeling and hypothesis testing</t>
+  </si>
+  <si>
+    <t>Tue, Jun 23</t>
+  </si>
+  <si>
+    <t>Reduction Technique</t>
+  </si>
+  <si>
+    <t>Causal Inference I</t>
+  </si>
+  <si>
+    <t>Workshop - Reduction technique: index building</t>
+  </si>
+  <si>
+    <t>2.5 hr</t>
+  </si>
+  <si>
+    <t>Dr. Huaiyang Zhong or Yang Cheng ??</t>
+  </si>
+  <si>
+    <t>Workshop - Causal Inference Philosophy and Introduction</t>
+  </si>
+  <si>
+    <t>Interns work on Project - Work on statistical modeling and apply index building techniques if applicable</t>
+  </si>
+  <si>
+    <t>Workshop - Causal Inference Methods - RCT, DID, Synthetic Control</t>
+  </si>
+  <si>
+    <t>Interns draft statistical models</t>
+  </si>
+  <si>
+    <t>Wed, Jun 24</t>
+  </si>
+  <si>
+    <t>Thu, Jun 25</t>
+  </si>
+  <si>
+    <t>Causal Inference II</t>
+  </si>
+  <si>
+    <t>Fri, Jun 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Week 5 Topic : Modeling Skills </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yujuan </t>
   </si>
   <si>
     <t xml:space="preserve">Timing </t>
   </si>
   <si>
-    <t xml:space="preserve">Advanced Data Visualizatio </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yuanyuan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explorotary analysis </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced R Shiny </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week 5 Topic : Modeling Skills </t>
-  </si>
-  <si>
     <t xml:space="preserve">Introduction to Statistics </t>
   </si>
   <si>
-    <t xml:space="preserve">Yujuan </t>
+    <t>Huaiyang, Yang Cheng</t>
   </si>
   <si>
     <t>Reduction technique -- index building</t>
   </si>
   <si>
-    <t>Huaiyang, Yang Cheng</t>
+    <t xml:space="preserve">Yujuan (Causal Inference Philosophy, DID , Synthetic Control , RCT) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pragati ( IV , RDD) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Causal Inference (Lecture 1 &amp;  2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potentially : Propensity Score etc. </t>
   </si>
   <si>
     <t xml:space="preserve">9 am - 11: 30 am </t>
   </si>
   <si>
-    <t xml:space="preserve">Causal Inference (Lecture 1 &amp;  2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yujuan (Causal Inference Philosophy, DID , Synthetic Control , RCT) </t>
+    <t xml:space="preserve"> may expand to 3 hr</t>
   </si>
   <si>
     <t xml:space="preserve">9 am - 11 am in two days </t>
   </si>
   <si>
-    <t xml:space="preserve"> may expand to 3 hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pragati ( IV , RDD) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potentially : Propensity Score etc. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Week 6 Topic: Advanced Skills and Topics </t>
   </si>
   <si>
@@ -590,22 +775,13 @@
   </si>
   <si>
     <t>Timing : 9 - 11</t>
-  </si>
-  <si>
-    <t>Finalize Github , prepare for final presentation at Summer VT Undergraduate Research Symposium, finalize Kohl Insights</t>
-  </si>
-  <si>
-    <t>Move into Dorm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check in at New Hall West for dorm assignment. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -638,31 +814,28 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -676,10 +849,9 @@
       <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -698,6 +870,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -712,7 +890,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -784,6 +962,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1120,17 +1301,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="1"/>
-    <col min="2" max="2" width="61.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="47.83203125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.6640625" style="1"/>
+    <col min="1" max="1" width="10.625" style="1"/>
+    <col min="2" max="2" width="61.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1141,7 +1322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1155,7 +1336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,7 +1347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1174,7 +1355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1182,7 +1363,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1190,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -1201,7 +1382,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1212,7 +1393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1223,7 +1404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
@@ -1234,15 +1415,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="30.75">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1256,7 +1437,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97929D-AD65-4CE9-BF8E-66086023685B}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1265,7 +1446,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74299BF2-7816-4D37-8F2E-A4AEC8FE33CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1274,51 +1455,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="60.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.1640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="10.6640625" style="9"/>
+    <col min="1" max="1" width="21.25" style="9" customWidth="1"/>
+    <col min="2" max="2" width="72.125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.75" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="40.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="10.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="9" t="s">
         <v>35</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>178</v>
+        <v>38</v>
       </c>
       <c r="C4" s="12">
         <v>0.52083333333333337</v>
@@ -1327,280 +1508,323 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B5" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6"/>
+    <row r="6" spans="1:6">
       <c r="A6" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="21.75" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="21.75" customHeight="1">
       <c r="A9" s="15"/>
       <c r="B9" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:6" ht="148.5" customHeight="1">
       <c r="A10" s="15"/>
       <c r="B10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1">
       <c r="B11" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1">
       <c r="B12" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="B15" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="63" customHeight="1">
       <c r="B16" s="18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1">
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
     </row>
-    <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="21" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="20"/>
       <c r="F20" s="13"/>
     </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="21"/>
       <c r="B21" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+        <v>43</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="21"/>
       <c r="B22" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="21"/>
       <c r="B23" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="21"/>
       <c r="B24" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="21"/>
       <c r="E25" s="22"/>
     </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="21"/>
       <c r="B26" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="21"/>
       <c r="B27" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="21"/>
       <c r="B28" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="21"/>
     </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="B31" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+    </row>
+    <row r="32" spans="1:7">
       <c r="B32" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="B33" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6"/>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+    </row>
+    <row r="36" spans="1:6">
       <c r="B36" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="C36" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="E36" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="B37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="B38" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6"/>
+    <row r="41" spans="1:6">
       <c r="A41" s="9" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
       <c r="B42" s="9" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1610,96 +1834,97 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
-  <dimension ref="A1:M54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M57"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="65.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="41.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="65.375" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="41.625" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="30.625" customWidth="1"/>
+    <col min="12" max="12" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75"/>
+    <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="17.25" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="15.75">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="15.75">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1707,45 +1932,45 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="15.75">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="15.75">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1753,59 +1978,59 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="15.75">
       <c r="A13" s="14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="15.75">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="26" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="15.75">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1813,398 +2038,434 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="15.75">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>100</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="15.75">
       <c r="A20" s="9"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
+      <c r="B20" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>103</v>
+      </c>
       <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>104</v>
+      </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
-      <c r="B22" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="15.75">
+      <c r="A21" s="9"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75">
+      <c r="A22" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75">
       <c r="A23" s="9"/>
-      <c r="B23" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75">
       <c r="A24" s="9"/>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
+      <c r="B24" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="15.75">
       <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="B25" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="15.75">
       <c r="A26" s="9"/>
-      <c r="B26" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="15.75">
       <c r="A27" s="9"/>
-      <c r="B27" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="B27" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="15.75">
       <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="B29" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>103</v>
+      </c>
       <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="E29" s="9" t="s">
+        <v>104</v>
+      </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="13"/>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="15.75">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75">
+      <c r="A31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="13"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75">
       <c r="A32" s="21"/>
-      <c r="B32" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="21" t="s">
+      <c r="B32" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="21"/>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="21"/>
       <c r="E33" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="F33" s="21"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="1:13" ht="15.75">
       <c r="A34" s="21"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="22"/>
+      <c r="B34" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="F34" s="9"/>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:13" ht="18.75" customHeight="1">
       <c r="A35" s="21"/>
-      <c r="B35" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="E35" s="22"/>
       <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75">
       <c r="A36" s="21"/>
-      <c r="B36" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75">
       <c r="A37" s="21"/>
       <c r="B37" s="9" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="15.75">
       <c r="A38" s="21"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
+      <c r="B38" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>103</v>
+      </c>
       <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+      <c r="E38" s="9" t="s">
+        <v>104</v>
+      </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
-      <c r="B40" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="15.75">
+      <c r="A39" s="21"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75">
+      <c r="A40" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75">
       <c r="A41" s="9"/>
-      <c r="B41" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="21" t="s">
+      <c r="B41" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" s="9"/>
+        <v>64</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="21"/>
       <c r="E42" s="9" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="15.75">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="15.75">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="15.75">
       <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>126</v>
+      </c>
       <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
+      <c r="E45" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="15.75">
       <c r="A46" s="9"/>
-      <c r="B46" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="15.75">
       <c r="A47" s="9"/>
-      <c r="B47" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" s="9" t="s">
+      <c r="B47" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="9"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+    </row>
+    <row r="48" spans="1:13" ht="15.75">
+      <c r="A48" s="9"/>
       <c r="B48" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" s="9"/>
+        <v>81</v>
+      </c>
       <c r="E48" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B49" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>96</v>
+        <v>82</v>
+      </c>
+      <c r="F48" s="9"/>
+    </row>
+    <row r="49" spans="1:5" ht="15.75">
+      <c r="B49" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
-        <v>122</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75">
+      <c r="B50" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75">
+      <c r="B51" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75">
+      <c r="B52" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75"/>
+    <row r="54" spans="1:5" ht="15.75"/>
+    <row r="55" spans="1:5" ht="15.75">
+      <c r="A55" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75">
+      <c r="B56" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="B57" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2214,511 +2475,543 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4375F624-6CA8-4BD1-8837-D674A15E3640}">
-  <dimension ref="A1:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" customWidth="1"/>
-    <col min="2" max="2" width="68.33203125" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.25" customWidth="1"/>
+    <col min="2" max="2" width="68.375" customWidth="1"/>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="28.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="42.875" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="15.75">
       <c r="A4" s="10" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="15.75">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
       <c r="A6" s="9"/>
-      <c r="B6" s="28" t="s">
-        <v>126</v>
+      <c r="B6" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="9"/>
-      <c r="B7" s="26" t="s">
-        <v>128</v>
+      <c r="B7" s="28" t="s">
+        <v>141</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="15.75">
       <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="B8" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="9"/>
-      <c r="B9" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="15.75">
       <c r="A10" s="9"/>
-      <c r="B10" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75">
       <c r="A11" s="9"/>
-      <c r="B11" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>96</v>
-      </c>
+      <c r="B11" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="15.75">
       <c r="A12" s="9"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="E12" s="9"/>
+      <c r="B12" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="15.75">
+      <c r="A13" s="9"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75">
+      <c r="A14" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75">
       <c r="A15" s="15"/>
-      <c r="B15" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="15"/>
-      <c r="B16" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="9"/>
+      <c r="B16" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>151</v>
+      </c>
       <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="E16" s="9" t="s">
+        <v>121</v>
+      </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
+    <row r="17" spans="1:6" ht="15.75">
+      <c r="A17" s="15"/>
+      <c r="B17" s="9" t="s">
+        <v>145</v>
+      </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="15.75">
       <c r="A18" s="9"/>
-      <c r="B18" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="15.75">
       <c r="A19" s="9"/>
-      <c r="B19" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75">
       <c r="A20" s="9"/>
-      <c r="B20" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>96</v>
-      </c>
+      <c r="B20" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75">
       <c r="A21" s="9"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="B21" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
-      <c r="B23" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75">
+      <c r="A22" s="9"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75">
+      <c r="A23" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75">
       <c r="A24" s="9"/>
-      <c r="B24" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" t="s">
-        <v>139</v>
-      </c>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75">
       <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>151</v>
+      </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="E25" t="s">
+        <v>155</v>
+      </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="15.75">
       <c r="A26" s="9"/>
-      <c r="B26" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.75">
       <c r="A27" s="9"/>
-      <c r="B27" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75">
       <c r="A28" s="9"/>
-      <c r="B28" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>96</v>
-      </c>
+      <c r="B28" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="15.75">
       <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="B29" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="15.75">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75">
+      <c r="A31" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75">
       <c r="A32" s="21"/>
-      <c r="B32" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B32" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75">
       <c r="A33" s="21"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+      <c r="B33" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>151</v>
+      </c>
       <c r="D33" s="9"/>
-      <c r="E33" s="22"/>
+      <c r="E33" s="9" t="s">
+        <v>159</v>
+      </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="15.75">
       <c r="A34" s="21"/>
-      <c r="B34" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+      <c r="E34" s="22"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="15.75">
       <c r="A35" s="21"/>
-      <c r="B35" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75">
       <c r="A36" s="21"/>
-      <c r="B36" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>96</v>
-      </c>
+      <c r="B36" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="15.75">
       <c r="A37" s="21"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+      <c r="B37" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B38" s="13" t="s">
+    <row r="38" spans="1:6" ht="15.75">
+      <c r="A38" s="21"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75">
+      <c r="A39" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75">
+      <c r="A40" s="9"/>
+      <c r="B40" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75">
+      <c r="A41" s="9"/>
+      <c r="B41" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" s="9"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F42" s="9"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75">
+      <c r="A44" s="9"/>
+      <c r="B44" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
-      <c r="B39" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9" t="s">
+      <c r="C45" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9" t="s">
+      <c r="D45" s="9"/>
+      <c r="E45" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" s="9"/>
+    </row>
+    <row r="46" spans="1:6" ht="15.75">
+      <c r="B46" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="9"/>
-      <c r="B42" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F43" s="9"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B44" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>81</v>
-      </c>
-      <c r="B47" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="4"/>
-    </row>
+      <c r="C46" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75">
+      <c r="A49" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="15.75">
+      <c r="B67" s="4"/>
+    </row>
+    <row r="78" spans="2:2" ht="15.75"/>
+    <row r="79" spans="2:2" ht="15.75"/>
+    <row r="80" spans="2:2" ht="15.75"/>
+    <row r="84" ht="15.75"/>
+    <row r="85" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2726,50 +3019,533 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E959A69-B699-4CFA-82E0-7BD72875D037}">
-  <dimension ref="A15:D21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F63"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="27.375" customWidth="1"/>
+    <col min="2" max="2" width="58.5" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="32.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" t="s">
-        <v>153</v>
-      </c>
-    </row>
+    <row r="1" spans="1:6" ht="15.75">
+      <c r="A1" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75">
+      <c r="A2" s="24"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75">
+      <c r="A3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75">
+      <c r="A4" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75">
+      <c r="A5" s="9"/>
+      <c r="B5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
+      <c r="A7" s="9"/>
+      <c r="B7" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75">
+      <c r="A8" s="9"/>
+      <c r="B8" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75">
+      <c r="A11" s="9"/>
+      <c r="B11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75">
+      <c r="A14" s="9"/>
+      <c r="B14" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75">
+      <c r="A15" s="9"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75">
+      <c r="A16" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75">
+      <c r="A17" s="15"/>
+      <c r="B17" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75">
+      <c r="A18" s="15"/>
+      <c r="B18" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75">
+      <c r="A19" s="15"/>
+      <c r="B19" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75">
+      <c r="A21" s="9"/>
+      <c r="B21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75">
+      <c r="A24" s="9"/>
+      <c r="B24" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75">
+      <c r="A25" s="9"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75">
+      <c r="A26" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75">
+      <c r="A27" s="9"/>
+      <c r="B27" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75">
+      <c r="A30" s="9"/>
+      <c r="B30" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="9"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75">
+      <c r="A33" s="9"/>
+      <c r="B33" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75">
+      <c r="A35" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75">
+      <c r="A36" s="21"/>
+      <c r="B36" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75">
+      <c r="A37" s="21"/>
+      <c r="B37" t="s">
+        <v>162</v>
+      </c>
+      <c r="C37" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75">
+      <c r="A38" s="21"/>
+      <c r="B38" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75">
+      <c r="A39" s="21"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="9"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75">
+      <c r="A40" s="21"/>
+      <c r="B40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75">
+      <c r="A41" s="21"/>
+      <c r="B41" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" s="9"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75">
+      <c r="A42" s="21"/>
+      <c r="B42" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F42" s="9"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75">
+      <c r="A43" s="21"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75">
+      <c r="A44" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75">
+      <c r="A45" s="9"/>
+      <c r="F45" s="9"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>191</v>
+      </c>
+      <c r="B47" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75"/>
+    <row r="59" ht="15.75"/>
+    <row r="62" ht="15.75"/>
+    <row r="63" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2777,69 +3553,569 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC185F-F58B-4882-BB6A-99C5A8DAD27D}">
-  <dimension ref="A14:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J71"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="32.5" customWidth="1"/>
-    <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.75" customWidth="1"/>
+    <col min="2" max="2" width="63" customWidth="1"/>
+    <col min="3" max="3" width="23.375" customWidth="1"/>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="7" max="7" width="55.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D15" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="24" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10"/>
+    <row r="3" spans="1:10">
+      <c r="A3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="9"/>
+      <c r="B5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="9"/>
+      <c r="B7" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="45.75">
+      <c r="A8" s="9"/>
+      <c r="B8" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="9"/>
+      <c r="B10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="15"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="G14" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="G15" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="I16" s="9"/>
+      <c r="J16" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="G17" t="s">
+        <v>210</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="9"/>
+      <c r="B19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="G19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="B21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="B22" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="9"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="9"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="9"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="9"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="9"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="9"/>
+    </row>
+    <row r="31" spans="1:10"/>
+    <row r="32" spans="1:10"/>
+    <row r="33" spans="1:5">
+      <c r="A33" s="21"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="20"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="21"/>
+      <c r="B35" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="21"/>
+      <c r="B36" s="9" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="C36" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="21"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="22"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="21"/>
+      <c r="B38" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="21"/>
+      <c r="B39" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="B40" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="9"/>
+      <c r="B43" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="9"/>
+      <c r="B44" t="s">
         <v>162</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C44" t="s">
         <v>163</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E20" t="s">
+      <c r="C45" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>167</v>
-      </c>
-    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="B47" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="B48" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="B49" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5"/>
+    <row r="51" spans="1:5"/>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>216</v>
+      </c>
+      <c r="B52" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="D53" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>219</v>
+      </c>
+      <c r="B54" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5"/>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>221</v>
+      </c>
+      <c r="B56" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="B57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" t="s">
+        <v>226</v>
+      </c>
+      <c r="E58" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5"/>
+    <row r="60" spans="1:5">
+      <c r="D60" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5"/>
+    <row r="62" spans="1:5"/>
+    <row r="63" spans="1:5"/>
+    <row r="64" spans="1:5"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2848,43 +4124,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5580AA-63C5-4A17-B275-34DB10D89DEB}">
   <dimension ref="A14:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="52.33203125" customWidth="1"/>
+    <col min="1" max="1" width="52.375" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2898,27 +4174,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08672E17-9FFE-4DB4-AF66-56E8BA384E79}">
   <dimension ref="A14:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="D15" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2929,13 +4205,22 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C2D4C5-F861-4F4B-9751-7CF6281C8800}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -3073,15 +4358,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3089,36 +4365,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunbeiwang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1173" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31698AAF-FD04-4466-9B80-BC349D3B273E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963588D3-C371-694A-9249-80352D5ACEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15980" yWindow="580" windowWidth="20680" windowHeight="20730" firstSheet="5" activeTab="5" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <t>Week 1</t>
   </si>
   <si>
-    <t>Onboarding and Basic Research skills</t>
-  </si>
-  <si>
     <t>Onboarding and Project Assignment</t>
   </si>
   <si>
@@ -776,12 +773,15 @@
   <si>
     <t>Timing : 9 - 11</t>
   </si>
+  <si>
+    <t xml:space="preserve">Onboarding </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1301,17 +1301,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="1"/>
-    <col min="2" max="2" width="61.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="47.875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="10.6640625" style="1"/>
+    <col min="2" max="2" width="61.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,108 +1322,108 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="1" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="1" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="1" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="30.75">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1437,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97929D-AD65-4CE9-BF8E-66086023685B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1446,7 +1446,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74299BF2-7816-4D37-8F2E-A4AEC8FE33CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1455,51 +1455,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.25" style="9" customWidth="1"/>
-    <col min="2" max="2" width="72.125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.75" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="40.75" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="10.625" style="9"/>
+    <col min="1" max="1" width="21.1640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="72.1640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="10.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="9" t="s">
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="C4" s="12">
         <v>0.52083333333333337</v>
@@ -1508,139 +1508,139 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6"/>
-    <row r="6" spans="1:6">
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="21.75" customHeight="1">
+    <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="21.75" customHeight="1">
+    <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
       <c r="B9" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" ht="148.5" customHeight="1">
+    <row r="10" spans="1:6" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="18" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="18" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1">
-      <c r="B11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="E11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="9" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1">
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="16" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1"/>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="B14" s="16" t="s">
-        <v>53</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="9" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="18" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="63" customHeight="1">
-      <c r="B16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="20.25" customHeight="1">
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
     </row>
-    <row r="18" spans="1:7" ht="21" customHeight="1">
+    <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>60</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>61</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>62</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="20"/>
       <c r="F20" s="13"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
@@ -1648,183 +1648,183 @@
       <c r="F21" s="16"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
       <c r="B22" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="E25" s="22"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="21"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="10" t="s">
+      <c r="B30" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>75</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B31" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="9" t="s">
+    </row>
+    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="B33" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="E33" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6"/>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="9" t="s">
+    </row>
+    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="E37" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="B38" s="9" t="s">
+      <c r="C38" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="E38" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="B39" s="9" t="s">
+      <c r="C39" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="9" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="40" spans="1:6"/>
-    <row r="41" spans="1:6">
-      <c r="A41" s="9" t="s">
+      <c r="B41" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B41" s="9" t="s">
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="9" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1">
-      <c r="B42" s="9" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1835,96 +1835,95 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
   <dimension ref="A1:M57"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" customWidth="1"/>
-    <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="41.625" customWidth="1"/>
-    <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="30.625" customWidth="1"/>
-    <col min="12" max="12" width="20.75" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="65.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="41.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75"/>
-    <row r="3" spans="1:6" ht="15.75">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.25" customHeight="1">
+    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>93</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>94</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1932,45 +1931,45 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1978,59 +1977,59 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:13" ht="15.75">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2038,45 +2037,45 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:13" ht="15.75">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:13" ht="15.75">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:13" ht="15.75">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -2084,12 +2083,12 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>109</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2097,47 +2096,47 @@
       <c r="F22" s="13"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="E25" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2145,45 +2144,45 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2191,12 +2190,12 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -2204,48 +2203,48 @@
       <c r="F31" s="13"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:13" ht="15.75">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" s="21"/>
       <c r="E33" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F33" s="21"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" ht="15.75">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:13" ht="18.75" customHeight="1">
+    <row r="35" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -2254,45 +2253,45 @@
       <c r="F35" s="9"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" ht="15.75">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:13" ht="15.75">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:13" ht="15.75">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:13" ht="15.75">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2300,85 +2299,85 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:13" ht="15.75">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
     </row>
-    <row r="41" spans="1:13" ht="15.75">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42" s="21"/>
       <c r="E42" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:13" ht="15.75">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>120</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:13" ht="15.75">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:13" ht="15.75">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -2386,86 +2385,84 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
       <c r="B47" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
     </row>
-    <row r="48" spans="1:13" ht="15.75">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="9"/>
       <c r="B48" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" s="9"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E48" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F48" s="9"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.75">
-      <c r="B49" s="9" t="s">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15.75">
-      <c r="B50" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="C50" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15.75">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.75">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B52" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>130</v>
       </c>
-      <c r="C52" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15.75"/>
-    <row r="54" spans="1:5" ht="15.75"/>
-    <row r="55" spans="1:5" ht="15.75">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>131</v>
       </c>
-      <c r="B55" t="s">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.75">
-      <c r="B56" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="B57" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2475,107 +2472,107 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4375F624-6CA8-4BD1-8837-D674A15E3640}">
-  <dimension ref="A1:F85"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.25" customWidth="1"/>
-    <col min="2" max="2" width="68.375" customWidth="1"/>
-    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="68.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42.875" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>136</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>137</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -2583,97 +2580,97 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>148</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>149</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="29" t="s">
         <v>150</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>151</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2681,44 +2678,44 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
@@ -2726,43 +2723,43 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>152</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>153</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2770,44 +2767,44 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2815,43 +2812,43 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>157</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="20"/>
       <c r="F31" s="13"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -2859,44 +2856,44 @@
       <c r="E34" s="22"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -2904,56 +2901,56 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>160</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>161</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="9"/>
       <c r="B40" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" t="s">
         <v>162</v>
       </c>
-      <c r="C41" t="s">
-        <v>163</v>
-      </c>
       <c r="E41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -2961,57 +2958,52 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16"/>
     </row>
-    <row r="45" spans="1:6" ht="15.75">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:6" ht="15.75">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B46" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="B49" s="25" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" ht="15.75">
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B67" s="4"/>
     </row>
-    <row r="78" spans="2:2" ht="15.75"/>
-    <row r="79" spans="2:2" ht="15.75"/>
-    <row r="80" spans="2:2" ht="15.75"/>
-    <row r="84" ht="15.75"/>
-    <row r="85" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3019,119 +3011,119 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E959A69-B699-4CFA-82E0-7BD72875D037}">
-  <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.375" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="58.5" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="32.625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:6" ht="15.75">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>169</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>170</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -3139,110 +3131,110 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>176</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>177</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -3250,160 +3242,160 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>181</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>182</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
       <c r="B33" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -3411,56 +3403,56 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>187</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
       <c r="E35" s="20"/>
       <c r="F35" s="13"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" t="s">
         <v>162</v>
       </c>
-      <c r="C37" t="s">
-        <v>163</v>
-      </c>
       <c r="E37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -3468,44 +3460,44 @@
       <c r="E39" s="22"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="21"/>
       <c r="B40" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="21"/>
       <c r="B41" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="B42" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="21"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -3513,39 +3505,35 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>189</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>190</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:6" ht="15.75">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" t="s">
         <v>191</v>
       </c>
-      <c r="B47" t="s">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="B48" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75"/>
-    <row r="59" ht="15.75"/>
-    <row r="62" ht="15.75"/>
-    <row r="63" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3554,217 +3542,217 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC185F-F58B-4882-BB6A-99C5A8DAD27D}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="63" customWidth="1"/>
-    <col min="3" max="3" width="23.375" customWidth="1"/>
-    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="7" max="7" width="55.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="2" spans="1:10"/>
-    <row r="3" spans="1:10">
-      <c r="A3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="10" t="s">
+      <c r="B4" s="23" t="s">
         <v>195</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>196</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="45.75">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>202</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>203</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="G15" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="H16" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="G17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -3775,347 +3763,347 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="G19" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B22" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
     </row>
-    <row r="31" spans="1:10"/>
-    <row r="32" spans="1:10"/>
-    <row r="33" spans="1:5">
+    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>214</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="20"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="22"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B40" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" t="s">
         <v>162</v>
       </c>
-      <c r="C44" t="s">
-        <v>163</v>
-      </c>
       <c r="E44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B47" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B49" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5"/>
-    <row r="51" spans="1:5"/>
-    <row r="52" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" t="s">
         <v>216</v>
       </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="53" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="D53" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
-      <c r="D53" t="s">
+    <row r="54" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>219</v>
       </c>
-      <c r="B54" t="s">
+    </row>
+    <row r="55" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="55" spans="1:5"/>
-    <row r="56" spans="1:5">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>221</v>
       </c>
-      <c r="B56" t="s">
+    </row>
+    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="B57" t="s">
+    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>224</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>225</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>226</v>
       </c>
-      <c r="E58" t="s">
+    </row>
+    <row r="59" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="D60" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="59" spans="1:5"/>
-    <row r="60" spans="1:5">
-      <c r="D60" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5"/>
-    <row r="62" spans="1:5"/>
-    <row r="63" spans="1:5"/>
-    <row r="64" spans="1:5"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
+    <row r="61" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4124,43 +4112,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5580AA-63C5-4A17-B275-34DB10D89DEB}">
   <dimension ref="A14:C19"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="52.375" customWidth="1"/>
+    <col min="1" max="1" width="52.33203125" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75">
-      <c r="A16" t="s">
+      <c r="B16" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" t="s">
         <v>231</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="C18" t="s">
         <v>233</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>235</v>
-      </c>
       <c r="C19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -4174,27 +4162,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08672E17-9FFE-4DB4-AF66-56E8BA384E79}">
   <dimension ref="A14:D15"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.25" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" t="s">
         <v>236</v>
-      </c>
-      <c r="B15" t="s">
-        <v>217</v>
-      </c>
-      <c r="D15" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4205,7 +4193,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C2D4C5-F861-4F4B-9751-7CF6281C8800}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4221,6 +4209,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -4358,20 +4352,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunbeiwang\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963588D3-C371-694A-9249-80352D5ACEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1173" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31698AAF-FD04-4466-9B80-BC349D3B273E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="15980" yWindow="580" windowWidth="20680" windowHeight="20730" firstSheet="5" activeTab="5" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -60,6 +60,9 @@
     <t>Week 1</t>
   </si>
   <si>
+    <t>Onboarding and Basic Research skills</t>
+  </si>
+  <si>
     <t>Onboarding and Project Assignment</t>
   </si>
   <si>
@@ -773,15 +776,12 @@
   <si>
     <t>Timing : 9 - 11</t>
   </si>
-  <si>
-    <t xml:space="preserve">Onboarding </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1301,17 +1301,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="1"/>
-    <col min="2" max="2" width="61.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="47.83203125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.6640625" style="1"/>
+    <col min="1" max="1" width="10.625" style="1"/>
+    <col min="2" max="2" width="61.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,108 +1322,108 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>237</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30.75">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1437,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97929D-AD65-4CE9-BF8E-66086023685B}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1446,7 +1446,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74299BF2-7816-4D37-8F2E-A4AEC8FE33CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1455,51 +1455,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="72.1640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="10.6640625" style="9"/>
+    <col min="1" max="1" width="21.25" style="9" customWidth="1"/>
+    <col min="2" max="2" width="72.125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.75" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="40.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="10.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="12">
         <v>0.52083333333333337</v>
@@ -1508,139 +1508,139 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6"/>
+    <row r="6" spans="1:6">
       <c r="A6" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="21.75" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="21.75" customHeight="1">
       <c r="A9" s="15"/>
       <c r="B9" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="148.5" customHeight="1">
       <c r="A10" s="15"/>
       <c r="B10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1">
       <c r="B11" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1">
       <c r="B12" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="B15" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="63" customHeight="1">
       <c r="B16" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1">
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
     </row>
-    <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="21" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="20"/>
       <c r="F20" s="13"/>
     </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="21"/>
       <c r="B21" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
@@ -1648,183 +1648,183 @@
       <c r="F21" s="16"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="21"/>
       <c r="B22" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="21"/>
       <c r="B23" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="21"/>
       <c r="B24" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="21"/>
       <c r="E25" s="22"/>
     </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="21"/>
       <c r="B26" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="21"/>
       <c r="B27" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="21"/>
       <c r="B28" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="21"/>
     </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="B31" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="B32" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="B33" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6"/>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="B36" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="B37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:6">
       <c r="B38" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6"/>
+    <row r="41" spans="1:6">
       <c r="A41" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
       <c r="B42" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1835,95 +1835,96 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="65.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="41.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="65.375" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="41.625" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="30.625" customWidth="1"/>
+    <col min="12" max="12" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75"/>
+    <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="17.25" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="15.75">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="15.75">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="15.75">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1931,45 +1932,45 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="15.75">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="15.75">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="15.75">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1977,59 +1978,59 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="15.75">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="15.75">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="15.75">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="15.75">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2037,45 +2038,45 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="15.75">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="15.75">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="15.75">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="15.75">
       <c r="A21" s="9"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -2083,12 +2084,12 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="15.75">
       <c r="A22" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2096,47 +2097,47 @@
       <c r="F22" s="13"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="15.75">
       <c r="A23" s="9"/>
       <c r="B23" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="15.75">
       <c r="A24" s="9"/>
       <c r="B24" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="15.75">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="15.75">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2144,45 +2145,45 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="15.75">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="15.75">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="15.75">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="15.75">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2190,12 +2191,12 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="15.75">
       <c r="A31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -2203,48 +2204,48 @@
       <c r="F31" s="13"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="15.75">
       <c r="A32" s="21"/>
       <c r="B32" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="15.75">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D33" s="21"/>
       <c r="E33" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F33" s="21"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="15.75">
       <c r="A34" s="21"/>
       <c r="B34" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="18.75" customHeight="1">
       <c r="A35" s="21"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -2253,45 +2254,45 @@
       <c r="F35" s="9"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="15.75">
       <c r="A36" s="21"/>
       <c r="B36" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="15.75">
       <c r="A37" s="21"/>
       <c r="B37" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="15.75">
       <c r="A38" s="21"/>
       <c r="B38" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="15.75">
       <c r="A39" s="21"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2299,85 +2300,85 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="15.75">
       <c r="A40" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ht="15.75">
       <c r="A41" s="9"/>
       <c r="B41" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="15.75">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D42" s="21"/>
       <c r="E42" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="15.75">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="15.75">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="15.75">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="15.75">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -2385,84 +2386,86 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="15.75">
       <c r="A47" s="9"/>
       <c r="B47" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="15.75">
       <c r="A48" s="9"/>
       <c r="B48" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="B49" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75">
       <c r="B50" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75">
       <c r="B51" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75">
       <c r="B52" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75"/>
+    <row r="54" spans="1:5" ht="15.75"/>
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75">
       <c r="B56" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="B57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2472,107 +2475,107 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4375F624-6CA8-4BD1-8837-D674A15E3640}">
-  <dimension ref="A1:F67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" customWidth="1"/>
-    <col min="2" max="2" width="68.33203125" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.25" customWidth="1"/>
+    <col min="2" max="2" width="68.375" customWidth="1"/>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="42.875" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="15.75">
       <c r="A4" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="15.75">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="15.75">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="15.75">
       <c r="A8" s="9"/>
       <c r="B8" s="26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -2580,97 +2583,97 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="15.75">
       <c r="A10" s="9"/>
       <c r="B10" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="15.75">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="15.75">
       <c r="A12" s="9"/>
       <c r="B12" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="15.75">
       <c r="A13" s="9"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="15.75">
       <c r="A14" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="15.75">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75">
       <c r="A17" s="15"/>
       <c r="B17" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="15.75">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2678,44 +2681,44 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="15.75">
       <c r="A19" s="9"/>
       <c r="B19" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.75">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75">
       <c r="A21" s="9"/>
       <c r="B21" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75">
       <c r="A22" s="9"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
@@ -2723,43 +2726,43 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="15.75">
       <c r="A23" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="15.75">
       <c r="A24" s="9"/>
       <c r="B24" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="15.75">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="15.75">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2767,44 +2770,44 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.75">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.75">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="15.75">
       <c r="A29" s="9"/>
       <c r="B29" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="15.75">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2812,43 +2815,43 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="15.75">
       <c r="A31" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="20"/>
       <c r="F31" s="13"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="15.75">
       <c r="A32" s="21"/>
       <c r="B32" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="15.75">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="15.75">
       <c r="A34" s="21"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -2856,44 +2859,44 @@
       <c r="E34" s="22"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="15.75">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="15.75">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="15.75">
       <c r="A37" s="21"/>
       <c r="B37" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="15.75">
       <c r="A38" s="21"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -2901,56 +2904,56 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="15.75">
       <c r="A39" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="15.75">
       <c r="A40" s="9"/>
       <c r="B40" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="15.75">
       <c r="A41" s="9"/>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="15.75">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="15.75">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -2958,52 +2961,57 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="15.75">
       <c r="A44" s="9"/>
       <c r="B44" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="15.75">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="15.75">
       <c r="B46" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75">
       <c r="A49" s="25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="15.75">
       <c r="B67" s="4"/>
     </row>
+    <row r="78" spans="2:2" ht="15.75"/>
+    <row r="79" spans="2:2" ht="15.75"/>
+    <row r="80" spans="2:2" ht="15.75"/>
+    <row r="84" ht="15.75"/>
+    <row r="85" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3011,119 +3019,119 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E959A69-B699-4CFA-82E0-7BD72875D037}">
-  <dimension ref="A1:F48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F63"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.375" customWidth="1"/>
     <col min="2" max="2" width="58.5" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
-    <col min="5" max="5" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="32.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="15.75">
       <c r="A4" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="15.75">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="15.75">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="15.75">
       <c r="A8" s="9"/>
       <c r="B8" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="15.75">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -3131,110 +3139,110 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="15.75">
       <c r="A11" s="9"/>
       <c r="B11" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="15.75">
       <c r="A12" s="9"/>
       <c r="B12" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="15.75">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="15.75">
       <c r="A14" s="9"/>
       <c r="B14" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="15.75">
       <c r="A15" s="9"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="15.75">
       <c r="A18" s="15"/>
       <c r="B18" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="15.75">
       <c r="A19" s="15"/>
       <c r="B19" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.75">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -3242,160 +3250,160 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75">
       <c r="A21" s="9"/>
       <c r="B21" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75">
       <c r="A22" s="9"/>
       <c r="B22" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="15.75">
       <c r="A23" s="9"/>
       <c r="B23" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="15.75">
       <c r="A24" s="9"/>
       <c r="B24" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="15.75">
       <c r="A25" s="9"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="15.75">
       <c r="A26" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.75">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.75">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="15.75">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="15.75">
       <c r="A30" s="9"/>
       <c r="B30" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="15.75">
       <c r="A31" s="9"/>
       <c r="B31" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="15.75">
       <c r="A32" s="9"/>
       <c r="B32" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="15.75">
       <c r="A33" s="9"/>
       <c r="B33" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="15.75">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -3403,56 +3411,56 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="15.75">
       <c r="A35" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
       <c r="E35" s="20"/>
       <c r="F35" s="13"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="15.75">
       <c r="A36" s="21"/>
       <c r="B36" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="15.75">
       <c r="A37" s="21"/>
       <c r="B37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="15.75">
       <c r="A38" s="21"/>
       <c r="B38" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="15.75">
       <c r="A39" s="21"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -3460,44 +3468,44 @@
       <c r="E39" s="22"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="15.75">
       <c r="A40" s="21"/>
       <c r="B40" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="15.75">
       <c r="A41" s="21"/>
       <c r="B41" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="15.75">
       <c r="A42" s="21"/>
       <c r="B42" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="15.75">
       <c r="A43" s="21"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -3505,35 +3513,39 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="15.75">
       <c r="A44" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="15.75">
       <c r="A45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B47" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" t="s">
-        <v>192</v>
-      </c>
-    </row>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75"/>
+    <row r="59" ht="15.75"/>
+    <row r="62" ht="15.75"/>
+    <row r="63" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3542,217 +3554,217 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC185F-F58B-4882-BB6A-99C5A8DAD27D}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="21.75" customWidth="1"/>
     <col min="2" max="2" width="63" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.375" customWidth="1"/>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="7" max="7" width="55.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="24" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10"/>
+    <row r="3" spans="1:10">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="45.75">
       <c r="A8" s="9"/>
       <c r="B8" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="9"/>
       <c r="B10" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="15"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="G15" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="9"/>
       <c r="B16" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="9"/>
       <c r="B17" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="G17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -3763,347 +3775,347 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="9"/>
       <c r="B19" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="G19" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="B21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="B22" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="9"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="10" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="9"/>
     </row>
-    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="9"/>
     </row>
-    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="9"/>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="9"/>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10"/>
+    <row r="32" spans="1:10"/>
+    <row r="33" spans="1:5">
       <c r="A33" s="21"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="20"/>
     </row>
-    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
     </row>
-    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="21"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="22"/>
     </row>
-    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5">
       <c r="A38" s="21"/>
       <c r="B38" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
     </row>
-    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5">
       <c r="A39" s="21"/>
       <c r="B39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="B40" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="A42" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
     </row>
-    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="A43" s="9"/>
       <c r="B43" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E44" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
-    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="B47" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="B48" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="B49" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5"/>
+    <row r="51" spans="1:5"/>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B52" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="D53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5"/>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="B57" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B58" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D58" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E58" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5"/>
+    <row r="60" spans="1:5">
       <c r="D60" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="16" x14ac:dyDescent="0.2"/>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5"/>
+    <row r="62" spans="1:5"/>
+    <row r="63" spans="1:5"/>
+    <row r="64" spans="1:5"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4112,43 +4124,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5580AA-63C5-4A17-B275-34DB10D89DEB}">
   <dimension ref="A14:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="52.33203125" customWidth="1"/>
+    <col min="1" max="1" width="52.375" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75">
       <c r="A16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C19" t="s">
         <v>234</v>
-      </c>
-      <c r="C19" t="s">
-        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -4162,27 +4174,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08672E17-9FFE-4DB4-AF66-56E8BA384E79}">
   <dimension ref="A14:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4193,7 +4205,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C2D4C5-F861-4F4B-9751-7CF6281C8800}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.95"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4209,12 +4221,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -4352,37 +4358,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunbeiwang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pragatidahal/dspg-2026-curriculum-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1173" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31698AAF-FD04-4466-9B80-BC349D3B273E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB06B30C-810C-2044-AB7A-3DF4D8D3A484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15980" yWindow="580" windowWidth="20680" windowHeight="20730" firstSheet="5" activeTab="5" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="8120" yWindow="600" windowWidth="20680" windowHeight="16100" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <t>Week 1</t>
   </si>
   <si>
-    <t>Onboarding and Basic Research skills</t>
-  </si>
-  <si>
     <t>Onboarding and Project Assignment</t>
   </si>
   <si>
@@ -776,12 +773,15 @@
   <si>
     <t>Timing : 9 - 11</t>
   </si>
+  <si>
+    <t>Onboarding and Basic Research skills</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -814,28 +814,31 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -849,6 +852,7 @@
       <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1301,17 +1305,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7D784-1E42-A348-A9E2-F410F7914403}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="1"/>
-    <col min="2" max="2" width="61.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="47.875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="10.6640625" style="1"/>
+    <col min="2" max="2" width="61.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,108 +1326,108 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="1" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="1" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="1" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="30.75">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1441,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97929D-AD65-4CE9-BF8E-66086023685B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1446,7 +1450,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74299BF2-7816-4D37-8F2E-A4AEC8FE33CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1455,51 +1459,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.25" style="9" customWidth="1"/>
-    <col min="2" max="2" width="72.125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.75" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="40.75" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="10.625" style="9"/>
+    <col min="1" max="1" width="21.1640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="72.1640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="10.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="9" t="s">
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="C4" s="12">
         <v>0.52083333333333337</v>
@@ -1508,139 +1512,139 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6"/>
-    <row r="6" spans="1:6">
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="21.75" customHeight="1">
+    <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="21.75" customHeight="1">
+    <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
       <c r="B9" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" ht="148.5" customHeight="1">
+    <row r="10" spans="1:6" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="18" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="18" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1">
-      <c r="B11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="E11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="9" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1">
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="16" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1"/>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="B14" s="16" t="s">
-        <v>53</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="9" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="18" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="63" customHeight="1">
-      <c r="B16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="20.25" customHeight="1">
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
     </row>
-    <row r="18" spans="1:7" ht="21" customHeight="1">
+    <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>60</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>61</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>62</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="20"/>
       <c r="F20" s="13"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
@@ -1648,183 +1652,183 @@
       <c r="F21" s="16"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
       <c r="B22" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="E25" s="22"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="21"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="10" t="s">
+      <c r="B30" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>75</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B31" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="9" t="s">
+    </row>
+    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="B33" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="E33" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6"/>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="9" t="s">
+    </row>
+    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="E37" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="B38" s="9" t="s">
+      <c r="C38" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="E38" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="B39" s="9" t="s">
+      <c r="C39" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="9" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="40" spans="1:6"/>
-    <row r="41" spans="1:6">
-      <c r="A41" s="9" t="s">
+      <c r="B41" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B41" s="9" t="s">
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="9" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1">
-      <c r="B42" s="9" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1835,96 +1839,95 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E724203-93BF-4AB3-BBFF-F621604F3060}">
   <dimension ref="A1:M57"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.625" customWidth="1"/>
-    <col min="2" max="2" width="65.375" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="41.625" customWidth="1"/>
-    <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="30.625" customWidth="1"/>
-    <col min="12" max="12" width="20.75" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="65.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="41.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75"/>
-    <row r="3" spans="1:6" ht="15.75">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.25" customHeight="1">
+    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>93</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>94</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1932,45 +1935,45 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1978,59 +1981,59 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:13" ht="15.75">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2038,45 +2041,45 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:13" ht="15.75">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:13" ht="15.75">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:13" ht="15.75">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
@@ -2084,12 +2087,12 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>109</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2097,47 +2100,47 @@
       <c r="F22" s="13"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="E25" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2145,45 +2148,45 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2191,12 +2194,12 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -2204,48 +2207,48 @@
       <c r="F31" s="13"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:13" ht="15.75">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" s="21"/>
       <c r="E33" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F33" s="21"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" ht="15.75">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:13" ht="18.75" customHeight="1">
+    <row r="35" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -2254,45 +2257,45 @@
       <c r="F35" s="9"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" ht="15.75">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:13" ht="15.75">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:13" ht="15.75">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:13" ht="15.75">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2300,85 +2303,85 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:13" ht="15.75">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
     </row>
-    <row r="41" spans="1:13" ht="15.75">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42" s="21"/>
       <c r="E42" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:13" ht="15.75">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>120</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:13" ht="15.75">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:13" ht="15.75">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -2386,86 +2389,84 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
       <c r="B47" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
     </row>
-    <row r="48" spans="1:13" ht="15.75">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="9"/>
       <c r="B48" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" s="9"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E48" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F48" s="9"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.75">
-      <c r="B49" s="9" t="s">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15.75">
-      <c r="B50" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="C50" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15.75">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.75">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B52" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>130</v>
       </c>
-      <c r="C52" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15.75"/>
-    <row r="54" spans="1:5" ht="15.75"/>
-    <row r="55" spans="1:5" ht="15.75">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>131</v>
       </c>
-      <c r="B55" t="s">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.75">
-      <c r="B56" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="B57" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2475,107 +2476,107 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4375F624-6CA8-4BD1-8837-D674A15E3640}">
-  <dimension ref="A1:F85"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.25" customWidth="1"/>
-    <col min="2" max="2" width="68.375" customWidth="1"/>
-    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="68.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42.875" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>136</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>137</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -2583,97 +2584,97 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>148</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>149</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="29" t="s">
         <v>150</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>151</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2681,44 +2682,44 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
@@ -2726,43 +2727,43 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>152</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>153</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2770,44 +2771,44 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2815,43 +2816,43 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>157</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="20"/>
       <c r="F31" s="13"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -2859,44 +2860,44 @@
       <c r="E34" s="22"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -2904,56 +2905,56 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>160</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>161</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="9"/>
       <c r="B40" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" t="s">
         <v>162</v>
       </c>
-      <c r="C41" t="s">
-        <v>163</v>
-      </c>
       <c r="E41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -2961,57 +2962,52 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16"/>
     </row>
-    <row r="45" spans="1:6" ht="15.75">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:6" ht="15.75">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B46" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="B49" s="25" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" ht="15.75">
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B67" s="4"/>
     </row>
-    <row r="78" spans="2:2" ht="15.75"/>
-    <row r="79" spans="2:2" ht="15.75"/>
-    <row r="80" spans="2:2" ht="15.75"/>
-    <row r="84" ht="15.75"/>
-    <row r="85" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3019,119 +3015,119 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E959A69-B699-4CFA-82E0-7BD72875D037}">
-  <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.375" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="58.5" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="32.625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:6" ht="15.75">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>169</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>170</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -3139,110 +3135,110 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>176</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>177</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -3250,160 +3246,160 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>181</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>182</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
       <c r="B33" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -3411,56 +3407,56 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>187</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
       <c r="E35" s="20"/>
       <c r="F35" s="13"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" t="s">
         <v>162</v>
       </c>
-      <c r="C37" t="s">
-        <v>163</v>
-      </c>
       <c r="E37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -3468,44 +3464,44 @@
       <c r="E39" s="22"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="21"/>
       <c r="B40" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="21"/>
       <c r="B41" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="B42" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="21"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -3513,39 +3509,35 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>189</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>190</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:6" ht="15.75">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" t="s">
         <v>191</v>
       </c>
-      <c r="B47" t="s">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="B48" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75"/>
-    <row r="59" ht="15.75"/>
-    <row r="62" ht="15.75"/>
-    <row r="63" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3554,217 +3546,217 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC185F-F58B-4882-BB6A-99C5A8DAD27D}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="63" customWidth="1"/>
-    <col min="3" max="3" width="23.375" customWidth="1"/>
-    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="7" max="7" width="55.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="2" spans="1:10"/>
-    <row r="3" spans="1:10">
-      <c r="A3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="10" t="s">
+      <c r="B4" s="23" t="s">
         <v>195</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>196</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="45.75">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>202</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>203</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="G15" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="H16" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="G17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -3775,347 +3767,347 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="G19" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B22" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
     </row>
-    <row r="31" spans="1:10"/>
-    <row r="32" spans="1:10"/>
-    <row r="33" spans="1:5">
+    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>214</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
       <c r="E34" s="20"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="22"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B40" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" t="s">
         <v>162</v>
       </c>
-      <c r="C44" t="s">
-        <v>163</v>
-      </c>
       <c r="E44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B47" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B49" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5"/>
-    <row r="51" spans="1:5"/>
-    <row r="52" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" t="s">
         <v>216</v>
       </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="53" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="D53" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
-      <c r="D53" t="s">
+    <row r="54" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>219</v>
       </c>
-      <c r="B54" t="s">
+    </row>
+    <row r="55" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="55" spans="1:5"/>
-    <row r="56" spans="1:5">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>221</v>
       </c>
-      <c r="B56" t="s">
+    </row>
+    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="B57" t="s">
+    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>224</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>225</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>226</v>
       </c>
-      <c r="E58" t="s">
+    </row>
+    <row r="59" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="D60" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="59" spans="1:5"/>
-    <row r="60" spans="1:5">
-      <c r="D60" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5"/>
-    <row r="62" spans="1:5"/>
-    <row r="63" spans="1:5"/>
-    <row r="64" spans="1:5"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
+    <row r="61" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:5" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4124,43 +4116,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5580AA-63C5-4A17-B275-34DB10D89DEB}">
   <dimension ref="A14:C19"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="52.375" customWidth="1"/>
+    <col min="1" max="1" width="52.33203125" customWidth="1"/>
     <col min="2" max="2" width="35.5" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75">
-      <c r="A16" t="s">
+      <c r="B16" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" t="s">
         <v>231</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="C18" t="s">
         <v>233</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>235</v>
-      </c>
       <c r="C19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -4174,27 +4166,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08672E17-9FFE-4DB4-AF66-56E8BA384E79}">
   <dimension ref="A14:D15"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.25" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" t="s">
         <v>236</v>
-      </c>
-      <c r="B15" t="s">
-        <v>217</v>
-      </c>
-      <c r="D15" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4205,7 +4197,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C2D4C5-F861-4F4B-9751-7CF6281C8800}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4365,13 +4357,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/curriculum-2026.xlsx
+++ b/curriculum-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virginiatech.sharepoint.com/sites/2026-Summer-DSPG-Planning/Shared Documents/General/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2526" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D88EC66-DE93-4F33-9365-8B503898E2BF}"/>
+  <xr:revisionPtr revIDLastSave="2612" documentId="13_ncr:1_{65F6ACF4-0E11-4456-A716-D1BBD8106E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA88BA9E-D519-4456-8131-F3B601AC181F}"/>
   <bookViews>
-    <workbookView xWindow="17720" yWindow="150" windowWidth="20680" windowHeight="20730" firstSheet="2" activeTab="1" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="1" xr2:uid="{53A63D6F-E822-9F49-8454-1C6D116A7C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="388">
   <si>
     <t>Weeks</t>
   </si>
@@ -214,120 +214,156 @@
     <t>Contact</t>
   </si>
   <si>
+    <t>Office Location</t>
+  </si>
+  <si>
+    <t>Office Hours</t>
+  </si>
+  <si>
+    <t>DSPG Director</t>
+  </si>
+  <si>
+    <t>Dr. Le Wang</t>
+  </si>
+  <si>
+    <t>Hutch 321B</t>
+  </si>
+  <si>
+    <t>Faculty Leads-Program Management</t>
+  </si>
+  <si>
+    <t>Dr. Michael Cary</t>
+  </si>
+  <si>
+    <t>Dr. Yujuan Gao</t>
+  </si>
+  <si>
+    <t>Curriculum Lead</t>
+  </si>
+  <si>
+    <t>Dr. Chunbei Wang</t>
+  </si>
+  <si>
+    <t>Hutch 321A</t>
+  </si>
+  <si>
+    <t>Graduate Fellows</t>
+  </si>
+  <si>
+    <t>Xiaoyi Zhao -  lead</t>
+  </si>
+  <si>
+    <t>xiaoyiz@vt.edu</t>
+  </si>
+  <si>
+    <t>Kohl Centre Hutch 320</t>
+  </si>
+  <si>
+    <t>Yuanyuan Wen</t>
+  </si>
+  <si>
+    <t>yuanyuanw@vt.edu</t>
+  </si>
+  <si>
+    <t>Pragati Dahal</t>
+  </si>
+  <si>
+    <t>pdahal@vt.edu</t>
+  </si>
+  <si>
+    <t>Angana Chatterjee</t>
+  </si>
+  <si>
+    <t>anganac@vt.edu</t>
+  </si>
+  <si>
+    <t>Suyog Gautam</t>
+  </si>
+  <si>
+    <t>suyoggtm@vt.edu</t>
+  </si>
+  <si>
+    <t>Xiaofan Zhu</t>
+  </si>
+  <si>
+    <t>zxiaofan@vt.edu</t>
+  </si>
+  <si>
+    <t>Faculty Advisors</t>
+  </si>
+  <si>
+    <t>Dr. Isabel Bradburn</t>
+  </si>
+  <si>
+    <t>Dr. Huaiyang Zhong</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Undergrad Interns + Grad Fellows + Faculty advisors</t>
+  </si>
+  <si>
+    <t>Project Team Assignment</t>
+  </si>
+  <si>
+    <t>Project 1 xxx</t>
+  </si>
+  <si>
+    <t>Project 2 xxx</t>
+  </si>
+  <si>
+    <t>Project 3 xxx</t>
+  </si>
+  <si>
+    <t>Project 4 xxx</t>
+  </si>
+  <si>
+    <t>Project 5 xxx</t>
+  </si>
+  <si>
+    <t>Work Space</t>
+  </si>
+  <si>
+    <t>Hutch 311</t>
+  </si>
+  <si>
+    <t>Hutch 221</t>
+  </si>
+  <si>
+    <t>Hutch 324</t>
+  </si>
+  <si>
+    <t>Hutch 322</t>
+  </si>
+  <si>
+    <t>Hutch 319B</t>
+  </si>
+  <si>
+    <t>Grad Fellows</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>Undergrad Interns</t>
+  </si>
+  <si>
+    <t>Week 1: Onboarding, Project Assignment, Introduction to Research</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Event/Activities</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Office Hours</t>
-  </si>
-  <si>
-    <t>DSPG Director</t>
-  </si>
-  <si>
-    <t>Dr. Le Wang</t>
-  </si>
-  <si>
-    <t>Faculty Leads-Program Management</t>
-  </si>
-  <si>
-    <t>Dr. Michael Cary</t>
-  </si>
-  <si>
-    <t>Dr. Yujuan Gao</t>
-  </si>
-  <si>
-    <t>Graduate Fellows</t>
-  </si>
-  <si>
-    <t>Xiaoyi Zhao -  lead</t>
-  </si>
-  <si>
-    <t>xiaoyiz@vt.edu</t>
-  </si>
-  <si>
-    <t>Yuanyuan Wen</t>
-  </si>
-  <si>
-    <t>yuanyuanw@vt.edu</t>
-  </si>
-  <si>
-    <t>Pragati Dahal</t>
-  </si>
-  <si>
-    <t>pdahal@vt.edu</t>
-  </si>
-  <si>
-    <t>Angana Chatterjee</t>
-  </si>
-  <si>
-    <t>anganac@vt.edu</t>
-  </si>
-  <si>
-    <t>Suyog Gautam</t>
-  </si>
-  <si>
-    <t>suyoggtm@vt.edu</t>
-  </si>
-  <si>
-    <t>Xiaofan Zhu</t>
-  </si>
-  <si>
-    <t>zxiaofan@vt.edu</t>
-  </si>
-  <si>
-    <t>Faculty Advisors</t>
-  </si>
-  <si>
-    <t>Dr. Isabel Bradburn</t>
-  </si>
-  <si>
-    <t>Dr. Huaiyang Zhong</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Undergrad Interns + Grad Fellows + Faculty advisors</t>
-  </si>
-  <si>
-    <t>Project Personnel Assignment</t>
-  </si>
-  <si>
-    <t>Project 1 xxx</t>
-  </si>
-  <si>
-    <t>Project 2 xxx</t>
-  </si>
-  <si>
-    <t>Project 3 xxx</t>
-  </si>
-  <si>
-    <t>Project 4 xxx</t>
-  </si>
-  <si>
-    <t>Project 5 xxx</t>
-  </si>
-  <si>
-    <t>Grad Fellows</t>
-  </si>
-  <si>
-    <t>xx</t>
-  </si>
-  <si>
-    <t>Undergrad Interns</t>
-  </si>
-  <si>
-    <t>Week 1: Onboarding, Project Assignment, Introduction to Research</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Event/Activities</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
     <t>Responsible Parties</t>
   </si>
   <si>
@@ -340,7 +376,7 @@
     <t>Check in at New Hall West for dorm assignment</t>
   </si>
   <si>
-    <t>Dr. Michael Cary send information</t>
+    <t>Dr. Michael Cary will send information</t>
   </si>
   <si>
     <t>Mon, May 25</t>
@@ -467,7 +503,7 @@
     <t>Workshop - How to conduct literature review</t>
   </si>
   <si>
-    <t>1.5 hour</t>
+    <t>8:30 AM - 10:00 AM</t>
   </si>
   <si>
     <t>Interns work on project 
@@ -497,6 +533,12 @@
       - develop a work plan</t>
   </si>
   <si>
+    <t>VCE-AI Project Stakeholder Meeting (prefers after 2:00; can meet from 10:00-2:00)</t>
+  </si>
+  <si>
+    <t>Cals Walks Project Stakeholder Meeting (12:00-3:00)</t>
+  </si>
+  <si>
     <t>Week 1 Deliverables:</t>
   </si>
   <si>
@@ -593,16 +635,13 @@
     <t>Workshop - Coding Organization &amp; Standard Template</t>
   </si>
   <si>
-    <t>1 hr</t>
-  </si>
-  <si>
     <t>Xiaoyi Zhao</t>
   </si>
   <si>
     <t>Workshop - Organizing and Documenting Data Availability</t>
   </si>
   <si>
-    <t>1/2 to 1 hr</t>
+    <t>10:00 AM - 11:00 AM</t>
   </si>
   <si>
     <t>Interns implement organization and documentation template</t>
@@ -677,7 +716,7 @@
     <t>Workshop - Structured and Large Dataset</t>
   </si>
   <si>
-    <t>2 hr</t>
+    <t>9:00 AM - 11:00 AM</t>
   </si>
   <si>
     <t>Wed, Jun 10</t>
@@ -717,6 +756,9 @@
   </si>
   <si>
     <t>Progress Report (10-15 minute presentation + 5-10 minutes Q&amp;A)</t>
+  </si>
+  <si>
+    <t>Hutch 302</t>
   </si>
   <si>
     <t>All Teams + Faculty</t>
@@ -751,7 +793,7 @@
     <t>Workshop - Reduction technique: index building</t>
   </si>
   <si>
-    <t>2.5 hr</t>
+    <t>9:00 AM - 11:30 AM</t>
   </si>
   <si>
     <t>Dr. Huaiyang Zhong or Yang Cheng ??</t>
@@ -771,9 +813,6 @@
     <t>Workshop - Advanced Data Visualization &amp; Exploratory Analysis</t>
   </si>
   <si>
-    <t>3 hr</t>
-  </si>
-  <si>
     <t>Wed, Jun 17</t>
   </si>
   <si>
@@ -783,7 +822,7 @@
     <t>Workshop - Advanced R Shiny</t>
   </si>
   <si>
-    <t>1.5 hr</t>
+    <t>9:00 AM - 10:30 AM</t>
   </si>
   <si>
     <t>Interns work on Project 
@@ -918,6 +957,9 @@
     <t>Workshop - LLM</t>
   </si>
   <si>
+    <t>1 hr</t>
+  </si>
+  <si>
     <t>???</t>
   </si>
   <si>
@@ -973,9 +1015,6 @@
   </si>
   <si>
     <t>Workshop - Poster and Latex</t>
-  </si>
-  <si>
-    <t>2hr</t>
   </si>
   <si>
     <t>Interns work on Project 
@@ -1120,9 +1159,6 @@
   </si>
   <si>
     <t>Interns practice poster presentation with Grad Fellows</t>
-  </si>
-  <si>
-    <t>10:00 AM - 11:00 AM</t>
   </si>
   <si>
     <t>Interns mock poster presentation with faculty leads</t>
@@ -1319,7 +1355,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1350,6 +1386,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1364,7 +1406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1481,6 +1523,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2069,29 +2117,29 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>29</v>
@@ -2103,7 +2151,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -2112,26 +2160,26 @@
     <row r="6" spans="1:5" ht="48.75" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="62.1">
       <c r="A7" s="9"/>
       <c r="B7" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2144,7 +2192,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -2153,25 +2201,25 @@
     <row r="10" spans="1:5" ht="62.1">
       <c r="A10" s="9"/>
       <c r="B10" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2180,7 +2228,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>29</v>
@@ -2192,7 +2240,7 @@
     <row r="14" spans="1:5">
       <c r="A14" s="5"/>
       <c r="B14" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -2201,13 +2249,13 @@
     <row r="15" spans="1:5" ht="62.1">
       <c r="A15" s="9"/>
       <c r="B15" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2220,7 +2268,7 @@
     <row r="17" spans="1:5">
       <c r="A17" s="9"/>
       <c r="B17" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -2229,25 +2277,25 @@
     <row r="18" spans="1:5" ht="62.1">
       <c r="A18" s="9"/>
       <c r="B18" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="B19" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2259,7 +2307,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>29</v>
@@ -2271,7 +2319,7 @@
     <row r="22" spans="1:5">
       <c r="A22" s="9"/>
       <c r="B22" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2280,13 +2328,13 @@
     <row r="23" spans="1:5" ht="62.1">
       <c r="A23" s="9"/>
       <c r="B23" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2299,7 +2347,7 @@
     <row r="25" spans="1:5">
       <c r="A25" s="9"/>
       <c r="B25" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -2308,26 +2356,26 @@
     <row r="26" spans="1:5" ht="51" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="7" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="9"/>
       <c r="B27" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2339,7 +2387,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>29</v>
@@ -2351,7 +2399,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="16"/>
       <c r="B30" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -2360,13 +2408,13 @@
     <row r="31" spans="1:5" ht="62.1">
       <c r="A31" s="16"/>
       <c r="B31" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2379,7 +2427,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="16"/>
       <c r="B33" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -2388,25 +2436,25 @@
     <row r="34" spans="1:5" ht="62.1">
       <c r="A34" s="16"/>
       <c r="B34" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="B35" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2415,7 +2463,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>29</v>
@@ -2426,7 +2474,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="B38" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -2434,25 +2482,27 @@
     </row>
     <row r="39" spans="1:5">
       <c r="B39" s="10" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="B40" s="9" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D40" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E40" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2463,7 +2513,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="B42" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -2471,14 +2521,14 @@
     </row>
     <row r="43" spans="1:5" ht="63.75" customHeight="1">
       <c r="B43" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="17.25" customHeight="1">
@@ -2489,49 +2539,49 @@
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="29" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="B49" s="10" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="B50" s="10" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="B51" s="10" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="B52" s="10" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="B53" s="30" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2554,29 +2604,29 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>29</v>
@@ -2588,7 +2638,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -2597,26 +2647,26 @@
     <row r="6" spans="1:5" ht="60.75" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="62.1">
       <c r="A7" s="9"/>
       <c r="B7" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2629,7 +2679,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -2638,14 +2688,14 @@
     <row r="10" spans="1:5" ht="62.1">
       <c r="A10" s="9"/>
       <c r="B10" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2657,13 +2707,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2672,7 +2722,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>29</v>
@@ -2684,7 +2734,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="5"/>
       <c r="B15" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -2693,13 +2743,13 @@
     <row r="16" spans="1:5" ht="62.1">
       <c r="A16" s="9"/>
       <c r="B16" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2712,7 +2762,7 @@
     <row r="18" spans="1:5">
       <c r="A18" s="9"/>
       <c r="B18" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -2721,14 +2771,14 @@
     <row r="19" spans="1:5" ht="64.5" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
@@ -2740,13 +2790,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2758,7 +2808,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>29</v>
@@ -2770,7 +2820,7 @@
     <row r="24" spans="1:5">
       <c r="A24" s="9"/>
       <c r="B24" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -2779,13 +2829,13 @@
     <row r="25" spans="1:5" ht="62.1">
       <c r="A25" s="9"/>
       <c r="B25" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2798,7 +2848,7 @@
     <row r="27" spans="1:5">
       <c r="A27" s="9"/>
       <c r="B27" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -2807,14 +2857,14 @@
     <row r="28" spans="1:5" ht="62.1">
       <c r="A28" s="9"/>
       <c r="B28" s="7" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2827,13 +2877,13 @@
     <row r="30" spans="1:5">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2845,10 +2895,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -2857,7 +2907,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="16"/>
       <c r="B33" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -2866,13 +2916,13 @@
     <row r="34" spans="1:5" ht="62.1">
       <c r="A34" s="16"/>
       <c r="B34" s="7" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2885,7 +2935,7 @@
     <row r="36" spans="1:5">
       <c r="A36" s="16"/>
       <c r="B36" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -2894,14 +2944,14 @@
     <row r="37" spans="1:5" ht="62.1">
       <c r="A37" s="16"/>
       <c r="B37" s="7" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2913,13 +2963,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="B39" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2928,10 +2978,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
@@ -2939,7 +2989,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="B42" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -2947,25 +2997,24 @@
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="10" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="B44" s="9" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" s="9"/>
+        <v>122</v>
+      </c>
       <c r="E44" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2976,7 +3025,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -2984,14 +3033,14 @@
     </row>
     <row r="47" spans="1:5" ht="62.1">
       <c r="B47" s="7" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -3002,31 +3051,31 @@
     </row>
     <row r="49" spans="1:5">
       <c r="B49" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="B53" s="10" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="B54" s="10" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3042,39 +3091,39 @@
     <col min="1" max="1" width="18.75" style="10" customWidth="1"/>
     <col min="2" max="2" width="66.125" style="10" customWidth="1"/>
     <col min="3" max="3" width="39.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="21.375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="10" customWidth="1"/>
     <col min="5" max="5" width="41" style="10" customWidth="1"/>
     <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -3083,7 +3132,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -3092,51 +3141,51 @@
     <row r="6" spans="1:5" ht="47.25" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="9"/>
       <c r="B7" s="7" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="9"/>
       <c r="B8" s="7" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>338</v>
+        <v>191</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="7" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3147,7 +3196,7 @@
     <row r="11" spans="1:5">
       <c r="A11" s="9"/>
       <c r="B11" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -3156,27 +3205,27 @@
     <row r="12" spans="1:5" ht="46.5">
       <c r="A12" s="9"/>
       <c r="B12" s="36" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3188,13 +3237,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3203,10 +3252,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3215,7 +3264,7 @@
     <row r="18" spans="1:5">
       <c r="A18" s="5"/>
       <c r="B18" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -3224,26 +3273,26 @@
     <row r="19" spans="1:5">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="9"/>
       <c r="B20" s="7" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3254,7 +3303,7 @@
     <row r="22" spans="1:5" ht="21.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -3263,27 +3312,27 @@
     <row r="23" spans="1:5">
       <c r="A23" s="9"/>
       <c r="B23" s="7" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3295,13 +3344,13 @@
     <row r="26" spans="1:5">
       <c r="A26" s="9"/>
       <c r="B26" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3312,10 +3361,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
@@ -3324,7 +3373,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="9"/>
       <c r="B29" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -3333,13 +3382,13 @@
     <row r="30" spans="1:5" ht="63.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="7" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3352,7 +3401,7 @@
     <row r="32" spans="1:5" ht="24" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -3361,10 +3410,10 @@
     <row r="33" spans="1:5" ht="19.5" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="7" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
@@ -3377,10 +3426,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -3389,31 +3438,31 @@
     <row r="36" spans="1:5">
       <c r="A36" s="9"/>
       <c r="B36" s="10" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C37" s="6">
         <v>0.72916666666666663</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3421,10 +3470,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
@@ -3432,7 +3481,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="B40" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -3440,52 +3489,52 @@
     </row>
     <row r="41" spans="1:5">
       <c r="B41" s="10" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="B42" s="10" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="10" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="B44" s="9" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="9" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C45" s="6">
         <v>0.47916666666666669</v>
@@ -3495,40 +3544,40 @@
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="9" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="29" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="B52" s="10" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="B53" s="10" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="B54" s="10" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="B55" s="10" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -3538,7 +3587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA26332-58FB-4B0D-9BEE-AFF3F3FCB780}">
-  <dimension ref="A2:F36"/>
+  <dimension ref="A2:F42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="35.625" style="10" customWidth="1"/>
@@ -3570,7 +3619,7 @@
       <c r="C3" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="29" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="22" t="s">
@@ -3584,307 +3633,376 @@
       <c r="B4" s="10" t="s">
         <v>58</v>
       </c>
+      <c r="D4" s="10" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="29"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="29"/>
       <c r="B7" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="29"/>
       <c r="B8" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.95">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30" t="s">
+      <c r="A9" s="29"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.95">
+      <c r="D10" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="29"/>
-      <c r="B11" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="17" t="s">
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="29" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.95">
-      <c r="A12" s="29"/>
-      <c r="B12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.95">
       <c r="A13" s="29"/>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="30" t="s">
         <v>69</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.95">
       <c r="A14" s="29"/>
       <c r="B14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>72</v>
+      <c r="D14" s="30" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.95">
       <c r="A15" s="29"/>
       <c r="B15" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="D15" s="30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.95">
+      <c r="A16" s="29"/>
+      <c r="B16" s="10" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="29" t="s">
+      <c r="C16" s="17" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="D16" s="30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.95">
       <c r="A17" s="29"/>
       <c r="B17" s="10" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="C17" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.95">
       <c r="A18" s="29"/>
       <c r="B18" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="29"/>
-      <c r="B19" s="10" t="s">
-        <v>60</v>
+      <c r="A19" s="29" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="29"/>
       <c r="B20" s="10" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="29"/>
       <c r="B21" s="10" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="29"/>
+      <c r="B22" s="10" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="29" t="s">
-        <v>78</v>
-      </c>
+      <c r="A23" s="29"/>
       <c r="B23" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="29"/>
+      <c r="B24" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="29"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="B26" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="29" t="s">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="31" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="29" t="s">
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="B31" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="C31" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="29"/>
-      <c r="B30" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="29"/>
+      <c r="D31" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="29"/>
+      <c r="B35" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="29"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C37" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D37" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E37" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F37" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="29"/>
-      <c r="B33" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="29"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="B36" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>87</v>
+    <row r="38" spans="1:6">
+      <c r="A38" s="29"/>
+      <c r="B38" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="29"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="29"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C15" r:id="rId1" display="mailto:zxiaofan@vt.edu" xr:uid="{602640B3-E802-4B7E-A06C-992541F5C40B}"/>
-    <hyperlink ref="C14" r:id="rId2" display="mailto:suyoggtm@vt.edu" xr:uid="{E81926C4-C6ED-46F8-A8A4-4FA43B6F7AD4}"/>
-    <hyperlink ref="C13" r:id="rId3" display="mailto:anganac@vt.edu" xr:uid="{ECFBB901-6897-44B6-BF87-7FF42FF7FF9D}"/>
-    <hyperlink ref="C12" r:id="rId4" display="mailto:pdahal@vt.edu" xr:uid="{6E0821F4-4441-456B-8158-D4A427E5494E}"/>
-    <hyperlink ref="C11" r:id="rId5" display="mailto:yuanyuanw@vt.edu" xr:uid="{847FF247-041A-400E-A39A-4A3461F61BBE}"/>
-    <hyperlink ref="C10" r:id="rId6" display="mailto:xiaoyiz@vt.edu" xr:uid="{8460B177-858F-4AD5-A5B6-CD0493A2D3E5}"/>
+    <hyperlink ref="C18" r:id="rId1" display="mailto:zxiaofan@vt.edu" xr:uid="{602640B3-E802-4B7E-A06C-992541F5C40B}"/>
+    <hyperlink ref="C17" r:id="rId2" display="mailto:suyoggtm@vt.edu" xr:uid="{E81926C4-C6ED-46F8-A8A4-4FA43B6F7AD4}"/>
+    <hyperlink ref="C16" r:id="rId3" display="mailto:anganac@vt.edu" xr:uid="{ECFBB901-6897-44B6-BF87-7FF42FF7FF9D}"/>
+    <hyperlink ref="C15" r:id="rId4" display="mailto:pdahal@vt.edu" xr:uid="{6E0821F4-4441-456B-8158-D4A427E5494E}"/>
+    <hyperlink ref="C14" r:id="rId5" display="mailto:yuanyuanw@vt.edu" xr:uid="{847FF247-041A-400E-A39A-4A3461F61BBE}"/>
+    <hyperlink ref="C13" r:id="rId6" display="mailto:xiaoyiz@vt.edu" xr:uid="{8460B177-858F-4AD5-A5B6-CD0493A2D3E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ABCE58-A8F1-4047-AD55-074F18A4BD46}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.25" style="9" customWidth="1"/>
     <col min="2" max="2" width="72.125" style="9" customWidth="1"/>
     <col min="3" max="3" width="18.75" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="22.25" style="9" customWidth="1"/>
     <col min="5" max="5" width="73.875" style="9" customWidth="1"/>
     <col min="6" max="16384" width="10.625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="18" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
@@ -3892,27 +4010,27 @@
     </row>
     <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6">
       <c r="A4" s="4" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="12"/>
@@ -3920,22 +4038,22 @@
     </row>
     <row r="5" spans="1:5" ht="15.6">
       <c r="B5" s="33" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C5" s="6">
         <v>0.52083333333333337</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.6"/>
     <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -3943,10 +4061,10 @@
     </row>
     <row r="9" spans="1:5" ht="21.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -3955,7 +4073,7 @@
     <row r="10" spans="1:5" ht="21.75" customHeight="1">
       <c r="A10" s="5"/>
       <c r="B10" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -3964,41 +4082,41 @@
     <row r="11" spans="1:5" ht="147" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="33" customHeight="1">
       <c r="B12" s="7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="19.5" customHeight="1">
       <c r="B13" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="19.5" customHeight="1"/>
     <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -4006,24 +4124,24 @@
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="B16" s="9" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="63" customHeight="1">
       <c r="B17" s="36" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="20.25" customHeight="1">
@@ -4032,10 +4150,10 @@
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -4043,10 +4161,10 @@
     </row>
     <row r="21" spans="1:6" ht="15.6">
       <c r="A21" s="4" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -4055,7 +4173,7 @@
     <row r="22" spans="1:6" ht="15.6">
       <c r="A22" s="16"/>
       <c r="B22" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -4065,10 +4183,13 @@
     <row r="23" spans="1:6" ht="15.6">
       <c r="A23" s="16"/>
       <c r="B23" s="9" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>124</v>
+        <v>136</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>58</v>
@@ -4077,13 +4198,16 @@
     <row r="24" spans="1:6" ht="15.6">
       <c r="A24" s="16"/>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>138</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.6">
@@ -4093,7 +4217,7 @@
     <row r="26" spans="1:6" ht="15.6">
       <c r="A26" s="16"/>
       <c r="B26" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -4102,13 +4226,13 @@
     <row r="27" spans="1:6" ht="62.1">
       <c r="A27" s="16"/>
       <c r="B27" s="36" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.6">
@@ -4116,10 +4240,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.6">
       <c r="A29" s="4" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
@@ -4127,7 +4251,7 @@
     </row>
     <row r="30" spans="1:6" ht="15.6">
       <c r="B30" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -4135,52 +4259,55 @@
     </row>
     <row r="31" spans="1:6" ht="15.6">
       <c r="B31" s="9" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>134</v>
+        <v>146</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30.95">
       <c r="B32" s="36" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.6">
       <c r="B33" s="33" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.95">
       <c r="B34" s="9" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.6"/>
     <row r="36" spans="1:5" ht="15.75" customHeight="1">
       <c r="B36" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -4188,43 +4315,53 @@
     </row>
     <row r="37" spans="1:5" ht="46.5">
       <c r="B37" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>142</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.6">
       <c r="B38" s="33" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15.6"/>
-    <row r="40" spans="1:5" ht="15.6">
-      <c r="A40" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" customHeight="1">
-      <c r="B41" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="B39" s="39" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="B40" s="39" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.6"/>
+    <row r="42" spans="1:5" ht="15.6">
+      <c r="A42" s="37" t="s">
+        <v>157</v>
+      </c>
       <c r="B42" s="9" t="s">
-        <v>146</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1">
+      <c r="B43" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1">
+      <c r="B44" s="9" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4243,7 +4380,7 @@
     <col min="1" max="1" width="18.375" style="10" customWidth="1"/>
     <col min="2" max="2" width="65.375" style="10" customWidth="1"/>
     <col min="3" max="3" width="18.75" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9" style="10"/>
+    <col min="4" max="4" width="24.875" style="10" customWidth="1"/>
     <col min="5" max="5" width="41.625" style="10" customWidth="1"/>
     <col min="6" max="7" width="9" style="10"/>
     <col min="8" max="8" width="30.625" style="10" customWidth="1"/>
@@ -4254,32 +4391,32 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -4288,7 +4425,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -4297,29 +4434,29 @@
     <row r="6" spans="1:5">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="9"/>
       <c r="B7" s="23" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4332,7 +4469,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -4341,27 +4478,27 @@
     <row r="10" spans="1:5">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4373,10 +4510,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -4385,7 +4522,7 @@
     <row r="14" spans="1:5">
       <c r="A14" s="5"/>
       <c r="B14" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -4394,29 +4531,29 @@
     <row r="15" spans="1:5">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5"/>
       <c r="B16" s="23" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -4429,7 +4566,7 @@
     <row r="18" spans="1:12">
       <c r="A18" s="9"/>
       <c r="B18" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -4438,27 +4575,27 @@
     <row r="19" spans="1:12">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -4470,10 +4607,10 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4483,7 +4620,7 @@
     <row r="23" spans="1:12">
       <c r="A23" s="9"/>
       <c r="B23" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -4492,29 +4629,29 @@
     <row r="24" spans="1:12">
       <c r="A24" s="9"/>
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4527,7 +4664,7 @@
     <row r="27" spans="1:12">
       <c r="A27" s="9"/>
       <c r="B27" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -4536,27 +4673,27 @@
     <row r="28" spans="1:12">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -4568,10 +4705,10 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="4" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -4581,7 +4718,7 @@
     <row r="32" spans="1:12">
       <c r="A32" s="16"/>
       <c r="B32" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -4590,30 +4727,30 @@
     <row r="33" spans="1:12">
       <c r="A33" s="16"/>
       <c r="B33" s="9" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="9" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L33" s="24"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="16"/>
       <c r="B34" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="18.75" customHeight="1">
@@ -4627,7 +4764,7 @@
     <row r="36" spans="1:12">
       <c r="A36" s="16"/>
       <c r="B36" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -4636,27 +4773,27 @@
     <row r="37" spans="1:12">
       <c r="A37" s="16"/>
       <c r="B37" s="9" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="16"/>
       <c r="B38" s="9" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -4668,10 +4805,10 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="4" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
@@ -4680,7 +4817,7 @@
     <row r="41" spans="1:12">
       <c r="A41" s="9"/>
       <c r="B41" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -4689,65 +4826,69 @@
     <row r="42" spans="1:12">
       <c r="A42" s="9"/>
       <c r="B42" s="9" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="9" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="9"/>
       <c r="B43" s="9" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="D43" s="9"/>
+        <v>119</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E43" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="D44" s="9"/>
+        <v>191</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E44" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="9"/>
       <c r="B46" s="33" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -4760,7 +4901,7 @@
     <row r="48" spans="1:12">
       <c r="A48" s="9"/>
       <c r="B48" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -4769,24 +4910,24 @@
     <row r="49" spans="1:5">
       <c r="A49" s="9"/>
       <c r="B49" s="9" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="B50" s="33" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4796,41 +4937,41 @@
     </row>
     <row r="52" spans="1:5">
       <c r="B52" s="10" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="B56" s="10" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="B57" s="10" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="B58" s="10" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="B59" s="30" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4853,32 +4994,32 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -4887,7 +5028,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -4896,27 +5037,27 @@
     <row r="6" spans="1:5" ht="62.1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="9"/>
       <c r="B7" s="23" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4929,7 +5070,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -4938,14 +5079,14 @@
     <row r="10" spans="1:5" ht="30.95">
       <c r="A10" s="9"/>
       <c r="B10" s="36" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4958,13 +5099,13 @@
     <row r="12" spans="1:5">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4973,10 +5114,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -4985,7 +5126,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="5"/>
       <c r="B15" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -4994,20 +5135,22 @@
     <row r="16" spans="1:5">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="D16" s="9"/>
+        <v>215</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E16" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30.95">
       <c r="A17" s="5"/>
       <c r="B17" s="36" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -5023,7 +5166,7 @@
     <row r="19" spans="1:5">
       <c r="A19" s="9"/>
       <c r="B19" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -5032,14 +5175,14 @@
     <row r="20" spans="1:5" ht="30.95">
       <c r="A20" s="9"/>
       <c r="B20" s="36" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5052,13 +5195,13 @@
     <row r="22" spans="1:5">
       <c r="A22" s="9"/>
       <c r="B22" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5070,10 +5213,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -5082,7 +5225,7 @@
     <row r="25" spans="1:5">
       <c r="A25" s="9"/>
       <c r="B25" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -5091,14 +5234,16 @@
     <row r="26" spans="1:5">
       <c r="A26" s="9"/>
       <c r="B26" s="9" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="10" t="s">
-        <v>206</v>
+        <v>215</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5111,7 +5256,7 @@
     <row r="28" spans="1:5">
       <c r="A28" s="9"/>
       <c r="B28" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -5120,14 +5265,14 @@
     <row r="29" spans="1:5" ht="30.95">
       <c r="A29" s="9"/>
       <c r="B29" s="36" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5140,13 +5285,13 @@
     <row r="31" spans="1:5">
       <c r="A31" s="9"/>
       <c r="B31" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5158,10 +5303,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="4" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -5170,7 +5315,7 @@
     <row r="34" spans="1:5">
       <c r="A34" s="16"/>
       <c r="B34" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -5179,14 +5324,16 @@
     <row r="35" spans="1:5">
       <c r="A35" s="16"/>
       <c r="B35" s="9" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9" t="s">
-        <v>210</v>
+        <v>215</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5199,7 +5346,7 @@
     <row r="37" spans="1:5">
       <c r="A37" s="16"/>
       <c r="B37" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -5208,14 +5355,14 @@
     <row r="38" spans="1:5" ht="30.95">
       <c r="A38" s="16"/>
       <c r="B38" s="36" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5228,13 +5375,13 @@
     <row r="40" spans="1:5">
       <c r="A40" s="16"/>
       <c r="B40" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -5246,10 +5393,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
@@ -5258,7 +5405,7 @@
     <row r="43" spans="1:5">
       <c r="A43" s="9"/>
       <c r="B43" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -5267,26 +5414,28 @@
     <row r="44" spans="1:5">
       <c r="A44" s="9"/>
       <c r="B44" s="10" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E45" s="9" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -5299,7 +5448,7 @@
     <row r="47" spans="1:5">
       <c r="A47" s="9"/>
       <c r="B47" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -5308,14 +5457,14 @@
     <row r="48" spans="1:5" ht="46.5">
       <c r="A48" s="9"/>
       <c r="B48" s="36" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5327,31 +5476,31 @@
     </row>
     <row r="50" spans="1:5">
       <c r="B50" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="29" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="B54" s="10" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="B55" s="30" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
     <row r="71" spans="2:2">
@@ -5377,7 +5526,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5385,27 +5534,27 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -5414,7 +5563,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -5423,27 +5572,29 @@
     <row r="6" spans="1:5" ht="46.5">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
-        <v>227</v>
+        <v>240</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5456,7 +5607,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -5465,26 +5616,26 @@
     <row r="10" spans="1:5" ht="46.5">
       <c r="A10" s="9"/>
       <c r="B10" s="36" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="9"/>
       <c r="B11" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5493,10 +5644,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -5505,7 +5656,7 @@
     <row r="14" spans="1:5">
       <c r="A14" s="5"/>
       <c r="B14" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -5514,14 +5665,16 @@
     <row r="15" spans="1:5">
       <c r="A15" s="5"/>
       <c r="B15" s="23" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="D15" s="9"/>
+        <v>167</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E15" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5534,7 +5687,7 @@
     <row r="17" spans="1:10">
       <c r="A17" s="9"/>
       <c r="B17" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -5543,14 +5696,14 @@
     <row r="18" spans="1:10" ht="54" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="36" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -5561,13 +5714,13 @@
     <row r="20" spans="1:10">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5576,10 +5729,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -5588,7 +5741,7 @@
     <row r="23" spans="1:10">
       <c r="A23" s="9"/>
       <c r="B23" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -5597,20 +5750,22 @@
     <row r="24" spans="1:10">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="D24" s="9"/>
+        <v>249</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E24" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="51" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="36" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -5634,7 +5789,7 @@
     <row r="27" spans="1:10">
       <c r="A27" s="9"/>
       <c r="B27" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -5643,14 +5798,14 @@
     <row r="28" spans="1:10" ht="43.5" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="36" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -5661,13 +5816,13 @@
     <row r="30" spans="1:10">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -5679,7 +5834,7 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>29</v>
@@ -5691,7 +5846,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="16"/>
       <c r="B33" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -5700,26 +5855,28 @@
     <row r="34" spans="1:5">
       <c r="A34" s="16"/>
       <c r="B34" s="10" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="16"/>
       <c r="B35" s="9" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E35" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5732,7 +5889,7 @@
     <row r="37" spans="1:5">
       <c r="A37" s="16"/>
       <c r="B37" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -5741,14 +5898,14 @@
     <row r="38" spans="1:5" ht="46.5">
       <c r="A38" s="16"/>
       <c r="B38" s="7" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5761,13 +5918,13 @@
     <row r="40" spans="1:5">
       <c r="A40" s="16"/>
       <c r="B40" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -5779,10 +5936,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
@@ -5793,20 +5950,20 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="29" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="10" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="B47" s="30" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -5831,33 +5988,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="22" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6"/>
     <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6">
       <c r="A4" s="4" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -5866,7 +6023,7 @@
     <row r="5" spans="1:5" ht="15.6">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -5875,27 +6032,29 @@
     <row r="6" spans="1:5" ht="51" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="46.5">
       <c r="A7" s="9"/>
       <c r="B7" s="7" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>167</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E7" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6">
@@ -5908,7 +6067,7 @@
     <row r="9" spans="1:5" ht="15.6">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -5917,14 +6076,14 @@
     <row r="10" spans="1:5" ht="30.95">
       <c r="A10" s="9"/>
       <c r="B10" s="36" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6">
@@ -5936,13 +6095,13 @@
     </row>
     <row r="12" spans="1:5" ht="15.6">
       <c r="B12" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6">
@@ -5951,10 +6110,10 @@
     </row>
     <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="4" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -5963,7 +6122,7 @@
     <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="5"/>
       <c r="B15" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -5972,22 +6131,24 @@
     <row r="16" spans="1:5" ht="30.95">
       <c r="A16" s="9"/>
       <c r="B16" s="36" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E16" s="9"/>
     </row>
     <row r="17" spans="1:5" ht="15.6">
       <c r="A17" s="9"/>
       <c r="B17" s="9" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E17" s="9" t="s">
         <v>58</v>
       </c>
@@ -6002,7 +6163,7 @@
     <row r="19" spans="1:5" ht="15.6">
       <c r="A19" s="9"/>
       <c r="B19" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -6011,27 +6172,29 @@
     <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="9"/>
+        <v>126</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E20" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="46.5">
       <c r="A21" s="9"/>
       <c r="B21" s="38" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.6">
@@ -6042,13 +6205,13 @@
     </row>
     <row r="23" spans="1:5" ht="15.6">
       <c r="B23" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.6">
@@ -6060,10 +6223,10 @@
     </row>
     <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="4" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -6072,7 +6235,7 @@
     <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="9"/>
       <c r="B26" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -6081,20 +6244,22 @@
     <row r="27" spans="1:5" ht="15.6">
       <c r="A27" s="9"/>
       <c r="B27" s="9" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="D27" s="9"/>
+        <v>215</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E27" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="46.5">
       <c r="A28" s="9"/>
       <c r="B28" s="38" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -6110,7 +6275,7 @@
     <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="9"/>
       <c r="B30" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -6119,14 +6284,14 @@
     <row r="31" spans="1:5" ht="46.5">
       <c r="A31" s="9"/>
       <c r="B31" s="38" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.6">
@@ -6138,13 +6303,13 @@
     <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.6">
@@ -6156,7 +6321,7 @@
     </row>
     <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="4" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>29</v>
@@ -6168,7 +6333,7 @@
     <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="16"/>
       <c r="B36" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -6177,14 +6342,14 @@
     <row r="37" spans="1:5" ht="46.5">
       <c r="A37" s="16"/>
       <c r="B37" s="38" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.6">
@@ -6197,7 +6362,7 @@
     <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="16"/>
       <c r="B39" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -6205,14 +6370,14 @@
     </row>
     <row r="40" spans="1:5" ht="46.5">
       <c r="B40" s="38" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.6">
@@ -6223,13 +6388,13 @@
     <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="9"/>
       <c r="B42" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.6">
@@ -6238,7 +6403,7 @@
     </row>
     <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="4" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>29</v>
@@ -6250,7 +6415,7 @@
     <row r="45" spans="1:5" ht="15.6">
       <c r="A45" s="9"/>
       <c r="B45" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -6259,26 +6424,28 @@
     <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="9"/>
       <c r="B46" s="10" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="9"/>
       <c r="B47" s="9" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E47" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.6">
@@ -6290,7 +6457,7 @@
     </row>
     <row r="49" spans="1:5" ht="15.6">
       <c r="B49" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -6298,14 +6465,14 @@
     </row>
     <row r="50" spans="1:5" ht="62.1">
       <c r="B50" s="26" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.6">
@@ -6316,28 +6483,28 @@
     </row>
     <row r="52" spans="1:5" ht="15.6">
       <c r="B52" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.6"/>
     <row r="54" spans="1:5" ht="15.6"/>
     <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="29" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.6">
       <c r="B56" s="30" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.6"/>
@@ -6377,32 +6544,32 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -6411,7 +6578,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -6420,27 +6587,29 @@
     <row r="6" spans="1:5" ht="50.25" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30.95">
       <c r="A7" s="9"/>
       <c r="B7" s="7" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>167</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E7" s="9" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6453,7 +6622,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -6462,14 +6631,14 @@
     <row r="10" spans="1:5" ht="30.95">
       <c r="A10" s="9"/>
       <c r="B10" s="36" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6481,13 +6650,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6496,10 +6665,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -6508,7 +6677,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="5"/>
       <c r="B15" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -6517,24 +6686,27 @@
     <row r="16" spans="1:5">
       <c r="A16" s="9"/>
       <c r="B16" s="9" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>276</v>
+        <v>289</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30.95">
       <c r="A17" s="9"/>
       <c r="B17" s="36" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6547,7 +6719,7 @@
     <row r="19" spans="1:5">
       <c r="A19" s="9"/>
       <c r="B19" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -6556,14 +6728,14 @@
     <row r="20" spans="1:5" ht="30.95">
       <c r="A20" s="9"/>
       <c r="B20" s="36" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6574,13 +6746,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="B22" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6592,10 +6764,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -6604,7 +6776,7 @@
     <row r="25" spans="1:5">
       <c r="A25" s="9"/>
       <c r="B25" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -6613,20 +6785,22 @@
     <row r="26" spans="1:5">
       <c r="A26" s="9"/>
       <c r="B26" s="9" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9" t="s">
-        <v>276</v>
+        <v>289</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="30.95">
       <c r="A27" s="9"/>
       <c r="B27" s="36" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -6635,14 +6809,14 @@
     <row r="28" spans="1:5">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6655,7 +6829,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="9"/>
       <c r="B30" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -6664,27 +6838,27 @@
     <row r="31" spans="1:5" ht="30.95">
       <c r="A31" s="9"/>
       <c r="B31" s="36" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="9"/>
       <c r="B32" s="9" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6697,13 +6871,13 @@
     <row r="34" spans="1:5">
       <c r="A34" s="9"/>
       <c r="B34" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -6715,7 +6889,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>29</v>
@@ -6727,7 +6901,7 @@
     <row r="37" spans="1:5">
       <c r="A37" s="16"/>
       <c r="B37" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -6736,26 +6910,28 @@
     <row r="38" spans="1:5">
       <c r="A38" s="16"/>
       <c r="B38" s="10" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="16"/>
       <c r="B39" s="9" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E39" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6768,7 +6944,7 @@
     <row r="41" spans="1:5">
       <c r="A41" s="16"/>
       <c r="B41" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -6776,26 +6952,26 @@
     </row>
     <row r="42" spans="1:5" ht="46.5">
       <c r="B42" s="36" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="9" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -6807,13 +6983,13 @@
     <row r="45" spans="1:5">
       <c r="A45" s="9"/>
       <c r="B45" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -6822,10 +6998,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="4" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
@@ -6833,20 +7009,20 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="29" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="B53" s="10" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="B54" s="30" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -6869,32 +7045,32 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="22" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -6903,7 +7079,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="9"/>
       <c r="B5" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -6912,27 +7088,29 @@
     <row r="6" spans="1:5" ht="49.5" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="19.5" customHeight="1">
       <c r="A7" s="9"/>
       <c r="B7" s="7" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>215</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E7" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6945,7 +7123,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="9"/>
       <c r="B9" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -6954,14 +7132,14 @@
     <row r="10" spans="1:5" ht="46.5">
       <c r="A10" s="9"/>
       <c r="B10" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6973,13 +7151,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6988,7 +7166,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>29</v>
@@ -7000,7 +7178,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="5"/>
       <c r="B15" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -7009,13 +7187,13 @@
     <row r="16" spans="1:5" ht="46.5">
       <c r="A16" s="9"/>
       <c r="B16" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7028,7 +7206,7 @@
     <row r="18" spans="1:5">
       <c r="A18" s="9"/>
       <c r="B18" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -7037,14 +7215,14 @@
     <row r="19" spans="1:5" ht="51" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="19.5" customHeight="1">
@@ -7056,13 +7234,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7074,7 +7252,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>29</v>
@@ -7086,7 +7264,7 @@
     <row r="24" spans="1:5">
       <c r="A24" s="9"/>
       <c r="B24" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -7095,13 +7273,13 @@
     <row r="25" spans="1:5" ht="46.5">
       <c r="A25" s="9"/>
       <c r="B25" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7114,7 +7292,7 @@
     <row r="27" spans="1:5">
       <c r="A27" s="9"/>
       <c r="B27" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -7123,14 +7301,14 @@
     <row r="28" spans="1:5" ht="46.5">
       <c r="A28" s="9"/>
       <c r="B28" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7143,13 +7321,13 @@
     <row r="30" spans="1:5">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7161,7 +7339,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>29</v>
@@ -7173,7 +7351,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="16"/>
       <c r="B33" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -7182,13 +7360,13 @@
     <row r="34" spans="1:5" ht="46.5">
       <c r="A34" s="16"/>
       <c r="B34" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7201,7 +7379,7 @@
     <row r="36" spans="1:5">
       <c r="A36" s="16"/>
       <c r="B36" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -7210,14 +7388,14 @@
     <row r="37" spans="1:5" ht="46.5">
       <c r="A37" s="16"/>
       <c r="B37" s="7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7229,13 +7407,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="B39" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -7244,7 +7422,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>29</v>
@@ -7255,7 +7433,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="B42" s="13" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -7263,25 +7441,27 @@
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="10" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="B44" s="9" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="E44" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -7292,7 +7472,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -7300,14 +7480,14 @@
     </row>
     <row r="47" spans="1:5" ht="46.5">
       <c r="B47" s="7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -7318,36 +7498,36 @@
     </row>
     <row r="49" spans="1:5">
       <c r="B49" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="B53" s="10" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="B54" s="10" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="B55" s="30" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -7362,6 +7542,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100411B9ADA3C88D84DA852962C88CCCF71" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb8c17446f1b3f0664823c0cd0cfd6e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29555bce-99f7-4351-a06e-6e58a2a8a9c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a69d9eff398ae5b3f2ca614c38d74f66" ns2:_="">
     <xsd:import namespace="29555bce-99f7-4351-a06e-6e58a2a8a9c5"/>
@@ -7499,23 +7688,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B2C08C-1A19-45F4-B774-B4C06928DC26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E948F4DD-3F9E-4963-820A-2F7ED559FDDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57BA70C-BAC7-4091-B4F1-876342C6970D}"/>
 </file>